--- a/docs/product/home-intelligence/requirements.xlsx
+++ b/docs/product/home-intelligence/requirements.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R81a7bad4a6bf4d28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求总表" sheetId="2" r:id="Rfc1a1ac72c8648dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira-Standard" sheetId="3" r:id="R312c90c4751c4f1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira-Advanced" sheetId="4" r:id="Rfa77d671ab5d4798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GitHub" sheetId="5" r:id="Rdeb32a65d46d47f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R1b9866e22be24457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rbb1a7c0aa6324eab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求总表" sheetId="2" r:id="R54dee4ac21c8436a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira-Standard" sheetId="3" r:id="Rbd22e690b4da48ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira-Advanced" sheetId="4" r:id="Rf6bd38cfd3514d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GitHub" sheetId="5" r:id="R5919784a4fa348a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R4632c4a09ad74b0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1569,7 +1569,7 @@
         <x:v>product:zhiwei,level:roadmap,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC2" s="91" t="str">
-        <x:v>ZW-PRD-001 §13</x:v>
+        <x:v>ZW-PRD-001 §13 Roadmap 与交付阶段</x:v>
       </x:c>
       <x:c r="AD2" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -1645,7 +1645,7 @@
         <x:v>product:zhiwei,level:roadmap,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC3" s="91" t="str">
-        <x:v>ZW-PRD-001 §13</x:v>
+        <x:v>ZW-PRD-001 §13 Roadmap 与交付阶段</x:v>
       </x:c>
       <x:c r="AD3" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -1721,7 +1721,7 @@
         <x:v>product:zhiwei,level:roadmap,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC4" s="91" t="str">
-        <x:v>ZW-PRD-001 §13</x:v>
+        <x:v>ZW-PRD-001 §13 Roadmap 与交付阶段</x:v>
       </x:c>
       <x:c r="AD4" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -1797,7 +1797,7 @@
         <x:v>product:zhiwei,level:roadmap,release:p3,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC5" s="91" t="str">
-        <x:v>ZW-PRD-001 §13</x:v>
+        <x:v>ZW-PRD-001 §13 Roadmap 与交付阶段</x:v>
       </x:c>
       <x:c r="AD5" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -1873,7 +1873,7 @@
         <x:v>product:zhiwei,level:roadmap,release:p4,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC6" s="91" t="str">
-        <x:v>ZW-PRD-001 §13</x:v>
+        <x:v>ZW-PRD-001 §13 Roadmap 与交付阶段</x:v>
       </x:c>
       <x:c r="AD6" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -1949,7 +1949,7 @@
         <x:v>product:zhiwei,level:roadmap,release:p0,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC7" s="91" t="str">
-        <x:v>ZW-PRD-001 §13</x:v>
+        <x:v>ZW-PRD-001 §13 Roadmap 与交付阶段</x:v>
       </x:c>
       <x:c r="AD7" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2033,7 +2033,7 @@
         <x:v>product:zhiwei,level:epic,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC8" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD8" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>product:zhiwei,level:epic,release:p0,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC9" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD9" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2197,7 +2197,7 @@
         <x:v>product:zhiwei,level:epic,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC10" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD10" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2281,7 +2281,7 @@
         <x:v>product:zhiwei,level:epic,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC11" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.2 网络拓扑</x:v>
       </x:c>
       <x:c r="AD11" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2365,7 +2365,7 @@
         <x:v>product:zhiwei,level:epic,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC12" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.1 设备总览</x:v>
       </x:c>
       <x:c r="AD12" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2449,7 +2449,7 @@
         <x:v>product:zhiwei,level:epic,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC13" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD13" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2533,7 +2533,7 @@
         <x:v>product:zhiwei,level:epic,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC14" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD14" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2617,7 +2617,7 @@
         <x:v>product:zhiwei,level:epic,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC15" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD15" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2701,7 +2701,7 @@
         <x:v>product:zhiwei,level:epic,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC16" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD16" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2785,7 +2785,7 @@
         <x:v>product:zhiwei,level:epic,release:p3,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC17" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD17" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2869,7 +2869,7 @@
         <x:v>product:zhiwei,level:epic,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC18" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD18" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -2951,7 +2951,7 @@
         <x:v>product:zhiwei,level:epic,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC19" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.4 任务队列</x:v>
       </x:c>
       <x:c r="AD19" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3033,7 +3033,7 @@
         <x:v>product:zhiwei,level:epic,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC20" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD20" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3115,7 +3115,7 @@
         <x:v>product:zhiwei,level:epic,release:p3,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC21" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD21" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3197,7 +3197,7 @@
         <x:v>product:zhiwei,level:epic,release:p4,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC22" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §5 用户与权限</x:v>
       </x:c>
       <x:c r="AD22" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3279,7 +3279,7 @@
         <x:v>product:zhiwei,level:epic,release:p3,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC23" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD23" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3361,7 +3361,7 @@
         <x:v>product:zhiwei,level:epic,release:p0,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC24" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §15 需求与交付追溯</x:v>
       </x:c>
       <x:c r="AD24" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3443,7 +3443,7 @@
         <x:v>product:zhiwei,level:epic,release:p1,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC25" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD25" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3515,7 +3515,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W26" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：建立多建筑多楼层空间树；检查“可创建、重命名、排序和停用空间节点”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X26" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -3533,7 +3533,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC26" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD26" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3607,7 +3607,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W27" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：按 Device Profile 添加设备；检查“向导依次完成模板选择、命名、参数、空间归属和连接验证”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X27" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -3625,7 +3625,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC27" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD27" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3699,7 +3699,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W28" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：编辑设备参数与空间归属；检查“保存后 device_id 不变”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X28" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -3717,7 +3717,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC28" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD28" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3791,7 +3791,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W29" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：设备详情渐进披露；检查“详情页展示状态、能力、任务历史和适配器信息”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X29" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -3809,7 +3809,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC29" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD29" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3879,7 +3879,7 @@
       </x:c>
       <x:c r="V30" s="92"/>
       <x:c r="W30" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：定义 Device Profile v0 契约；检查“Schema 覆盖本 PRD 的 12 类交互”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X30" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -3897,7 +3897,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC30" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD30" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -3969,7 +3969,7 @@
       </x:c>
       <x:c r="V31" s="92"/>
       <x:c r="W31" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：注册设备能力并供 UI 查询；检查“API 返回 capability_id、动作、参数、权限、风险和状态 Schema”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X31" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -3987,7 +3987,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC31" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD31" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4059,7 +4059,7 @@
       </x:c>
       <x:c r="V32" s="92"/>
       <x:c r="W32" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：建立家庭 Ontology v0；检查“Ontology 有版本和迁移记录”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X32" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4077,7 +4077,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC32" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD32" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4149,7 +4149,7 @@
       </x:c>
       <x:c r="V33" s="92"/>
       <x:c r="W33" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：能力 Schema 兼容迁移；检查“升级前给出兼容性检查”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X33" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4167,7 +4167,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC33" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD33" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4211,7 +4211,7 @@
         <x:v>作为家庭成员，我打开首页时能看到设备状态和状态时间。</x:v>
       </x:c>
       <x:c r="M34" s="92" t="str">
-        <x:v>局域网目标 2 秒内返回快照；每个状态含 observed_at 和 freshness；不可用值显示未知而非 0。</x:v>
+        <x:v>局域网目标 2 秒内返回快照；每个状态含 observed_at 和 freshness；不可用值显示未知而非 0；在目标环境采样中，95% 在线设备状态在定义的心跳窗口内更新。</x:v>
       </x:c>
       <x:c r="N34" s="92" t="str">
         <x:v>不包含未写入验收标准的扩展能力。</x:v>
@@ -4239,7 +4239,7 @@
       </x:c>
       <x:c r="V34" s="92"/>
       <x:c r="W34" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：读取家庭状态快照；检查“局域网目标 2 秒内返回快照”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X34" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4257,7 +4257,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC34" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD34" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4329,7 +4329,7 @@
       </x:c>
       <x:c r="V35" s="92"/>
       <x:c r="W35" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：订阅设备与任务事件；检查“SSE 或等价事件流支持断线重连和游标续传”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X35" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4347,7 +4347,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC35" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD35" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4419,7 +4419,7 @@
       </x:c>
       <x:c r="V36" s="92"/>
       <x:c r="W36" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：离线设备浅灰遮罩；检查“离线判定使用心跳窗口”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X36" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4437,7 +4437,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC36" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD36" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4481,7 +4481,7 @@
         <x:v>作为家庭成员，我能分辨系统正在尝试的状态和设备已确认的状态。</x:v>
       </x:c>
       <x:c r="M37" s="92" t="str">
-        <x:v>任务运行时展示 pending/running；只在设备上报或回查成功后更新 confirmed state；超时显示不确定。</x:v>
+        <x:v>任务运行时展示 pending/running；只在设备上报或回查成功后更新 confirmed state；超时显示不确定；任务“成功”与设备真实状态一致率 ≥ 99%。</x:v>
       </x:c>
       <x:c r="N37" s="92" t="str">
         <x:v>不包含未写入验收标准的扩展能力。</x:v>
@@ -4509,7 +4509,7 @@
       </x:c>
       <x:c r="V37" s="92"/>
       <x:c r="W37" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：区分期望状态与确认状态；检查“任务运行时展示 pending/running”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X37" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4527,7 +4527,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC37" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD37" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4601,7 +4601,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W38" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：展示家庭网络拓扑；检查“拓扑支持父子链路、连接类型和节点状态”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X38" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4619,7 +4619,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC38" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.2 网络拓扑</x:v>
       </x:c>
       <x:c r="AD38" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4693,7 +4693,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W39" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：查看网络节点健康度；检查“节点详情字段来源明确”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X39" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4711,7 +4711,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC39" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.2 网络拓扑</x:v>
       </x:c>
       <x:c r="AD39" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4785,7 +4785,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W40" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：从拓扑进入设备详情；检查“有关联 device_id 的节点可打开设备详情”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X40" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4803,7 +4803,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC40" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.2 网络拓扑</x:v>
       </x:c>
       <x:c r="AD40" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4847,7 +4847,7 @@
         <x:v>作为家庭成员，我能按房间扫描所有关键设备和状态。</x:v>
       </x:c>
       <x:c r="M41" s="92" t="str">
-        <x:v>卡片按建筑/楼层/房间稳定排序；房间标题显示聚合状态；未归属设备进入待整理分组。</x:v>
+        <x:v>卡片按建筑/楼层/房间稳定排序；房间标题显示聚合状态；未归属设备进入待整理分组；80% 的常用动作可在首页两次交互内完成。</x:v>
       </x:c>
       <x:c r="N41" s="92" t="str">
         <x:v>不包含未写入验收标准的扩展能力。</x:v>
@@ -4877,7 +4877,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W41" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：按房间归类首页卡片；检查“卡片按建筑/楼层/房间稳定排序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X41" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4895,7 +4895,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC41" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.1 设备总览</x:v>
       </x:c>
       <x:c r="AD41" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -4969,7 +4969,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W42" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：有限尺寸 Widget 网格；检查“仅允许预定义尺寸”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X42" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -4987,7 +4987,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC42" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.1 设备总览</x:v>
       </x:c>
       <x:c r="AD42" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5061,7 +5061,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W43" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：卡片与户型图二级视图；检查“默认进入卡片视图”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X43" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5079,7 +5079,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC43" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.1 设备总览</x:v>
       </x:c>
       <x:c r="AD43" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5153,7 +5153,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W44" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：空调温度步进控件；检查“控件显示允许范围”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X44" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5171,7 +5171,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC44" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD44" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5245,7 +5245,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W45" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：可调灯开关与亮度滑条；检查“开关关闭时滑条隐藏”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X45" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5263,7 +5263,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC45" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD45" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5337,7 +5337,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W46" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：对开窗帘开停关交互；检查“打开完成显示 0%，关闭完成显示 100%”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X46" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5355,7 +5355,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC46" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD46" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5429,7 +5429,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W47" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：卷帘开停关交互；检查“开为 0%、关为 100%”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X47" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5447,7 +5447,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC47" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD47" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5521,7 +5521,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W48" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：鱼缸灯光与投食交互；检查“投食期间按钮显示旋转状态且不可重复提交”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X48" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5539,7 +5539,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC48" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD48" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5613,7 +5613,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W49" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：智能插座与用电统计；检查“统计口径和更新时间可见”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X49" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5631,7 +5631,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC49" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD49" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5705,7 +5705,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W50" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：路由器安全重启；检查“点击后显示影响范围与预计离线时间”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X50" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5723,7 +5723,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC50" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD50" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5797,7 +5797,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W51" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：扫地机器人全屋清洁快捷操作；检查“首页仅有全屋清洁”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X51" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5815,7 +5815,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC51" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD51" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5889,7 +5889,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W52" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：长按语音设备指令；检查“界面明确提示按住说话”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X52" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5907,7 +5907,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC52" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD52" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -5981,7 +5981,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W53" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：个人电子设备只读状态；检查“卡片仅展示在线、网络和最后心跳”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X53" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -5999,7 +5999,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC53" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD53" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6073,7 +6073,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W54" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：中枢额度与数据中心指标卡；检查“额度显示 5 小时、周限额和预充值余额及更新时间”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X54" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6091,7 +6091,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC54" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD54" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6165,7 +6165,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W55" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：四档响应式网格；检查“折叠外屏压缩为单列重点信息”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X55" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6183,7 +6183,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC55" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD55" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6257,7 +6257,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W56" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：无限信息流与侧边栏版权；检查“主内容自然滚动”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X56" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6275,7 +6275,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC56" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD56" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6349,7 +6349,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W57" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：键盘、读屏与减少动态效果；检查“控件有可访问名称和焦点顺序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X57" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6367,7 +6367,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC57" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD57" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6441,7 +6441,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W58" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：添加单设备动作卡；检查“只能选择设备已注册的动作”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X58" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6459,7 +6459,7 @@
         <x:v>product:zhiwei,level:story,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC58" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD58" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6533,7 +6533,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W59" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：在一张卡中组合并行动作；检查“同卡动作无依赖时并行执行”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X59" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6551,7 +6551,7 @@
         <x:v>product:zhiwei,level:story,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC59" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD59" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6625,7 +6625,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W60" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：步骤排序与依赖校验；检查“支持拖动和键盘排序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X60" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6643,7 +6643,7 @@
         <x:v>product:zhiwei,level:story,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC60" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD60" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6717,7 +6717,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W61" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>组件/可访问性/响应式测试：场景草稿、Review 与发布；检查“草稿和已发布版本分离”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X61" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6735,7 +6735,7 @@
         <x:v>product:zhiwei,level:story,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC61" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD61" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6809,7 +6809,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W62" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>场景走查/指标验收：观影模式预置场景；检查“包含窗帘、灯、电视、Apple TV/Infuse、NAS 推荐和语音播报”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X62" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6827,7 +6827,7 @@
         <x:v>product:zhiwei,level:story,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC62" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD62" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6901,7 +6901,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W63" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>场景走查/指标验收：离家模式预置场景；检查“按能力发现目标而非写死设备清单”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X63" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -6919,7 +6919,7 @@
         <x:v>product:zhiwei,level:story,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC63" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD63" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -6993,7 +6993,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W64" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>计划评测/权限/工具集成测试：自然语言生成场景草稿；检查“系统展示解析出的意图、设备、动作和假设”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X64" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7011,7 +7011,7 @@
         <x:v>product:zhiwei,level:story,release:p3,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC64" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD64" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7085,7 +7085,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W65" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>计划评测/权限/工具集成测试：Skill 匹配与 Plan Mode 分流；检查“路由结果含匹配依据和置信度”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X65" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7103,7 +7103,7 @@
         <x:v>product:zhiwei,level:story,release:p3,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC65" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD65" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7177,7 +7177,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W66" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>计划评测/权限/工具集成测试：下载电影长程工作流；检查“计划调用 NAS 搜索 MCP、过滤候选、下载 MCP、等待完成和微信通知”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X66" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7195,7 +7195,7 @@
         <x:v>product:zhiwei,level:story,release:p3,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC66" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD66" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7239,7 +7239,7 @@
         <x:v>作为家庭成员，我触发场景后能看到每张卡和卡内动作的实时状态。</x:v>
       </x:c>
       <x:c r="M67" s="92" t="str">
-        <x:v>状态包含等待、运行、成功、失败、跳过和待确认；页面刷新后能恢复同一运行实例。</x:v>
+        <x:v>状态包含等待、运行、成功、失败、跳过和待确认；页面刷新后能恢复同一运行实例；已发布场景完整执行成功率 ≥ 95%，失败步骤可定位。</x:v>
       </x:c>
       <x:c r="N67" s="92" t="str">
         <x:v>不包含未写入验收标准的扩展能力。</x:v>
@@ -7269,7 +7269,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W67" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：逐卡执行并展示结果；检查“状态包含等待、运行、成功、失败、跳过和待确认”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X67" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7287,7 +7287,7 @@
         <x:v>product:zhiwei,level:story,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC67" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD67" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7361,7 +7361,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W68" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：失败策略、重试与取消；检查“错误码映射为可行动说明”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X68" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7379,7 +7379,7 @@
         <x:v>product:zhiwei,level:story,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC68" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD68" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7453,7 +7453,7 @@
         <x:v>apps/home-intelligence-web/app/page.tsx</x:v>
       </x:c>
       <x:c r="W69" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：长程流程断点续跑；检查“关键节点写入 checkpointer”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X69" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7471,7 +7471,7 @@
         <x:v>product:zhiwei,level:story,release:p2,roadmap:zw-rm-03</x:v>
       </x:c>
       <x:c r="AC69" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.3 场景与流程</x:v>
       </x:c>
       <x:c r="AD69" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7543,7 +7543,7 @@
       </x:c>
       <x:c r="V70" s="92"/>
       <x:c r="W70" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：统一异步任务契约；检查“任务含 idempotency_key、发起者、目标、参数、风险、超时、重试、trace_id 和标准状态机”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X70" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7561,7 +7561,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC70" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.4 任务队列</x:v>
       </x:c>
       <x:c r="AD70" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7633,7 +7633,7 @@
       </x:c>
       <x:c r="V71" s="92"/>
       <x:c r="W71" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：优先队列强制状态上报；检查“优先队列拒绝同步任务”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X71" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7651,7 +7651,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC71" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.4 任务队列</x:v>
       </x:c>
       <x:c r="AD71" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7723,7 +7723,7 @@
       </x:c>
       <x:c r="V72" s="92"/>
       <x:c r="W72" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：超时、重试和死信恢复；检查“重试次数与退避可配置”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X72" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7741,7 +7741,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC72" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.4 任务队列</x:v>
       </x:c>
       <x:c r="AD72" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7813,7 +7813,7 @@
       </x:c>
       <x:c r="V73" s="92"/>
       <x:c r="W73" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：任务队列双视图；检查“两类队列可筛选”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X73" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7831,7 +7831,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC73" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §7.4 任务队列</x:v>
       </x:c>
       <x:c r="AD73" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7903,7 +7903,7 @@
       </x:c>
       <x:c r="V74" s="92"/>
       <x:c r="W74" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：MCP 工具发现与能力白名单；检查“网关按身份、角色、设备和风险返回白名单”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X74" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -7921,7 +7921,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC74" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD74" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -7993,7 +7993,7 @@
       </x:c>
       <x:c r="V75" s="92"/>
       <x:c r="W75" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：设备适配器标准接口；检查“接口有契约测试”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X75" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8011,7 +8011,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC75" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD75" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8083,7 +8083,7 @@
       </x:c>
       <x:c r="V76" s="92"/>
       <x:c r="W76" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>契约/集成/故障测试：首批真实服务与设备接入；检查“至少 5 类真实接入通过读写/只读能力声明”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X76" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8101,7 +8101,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC76" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD76" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8173,7 +8173,7 @@
       </x:c>
       <x:c r="V77" s="92"/>
       <x:c r="W77" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>计划评测/权限/工具集成测试：意图与风险分级；检查“分类结果可解释且进入审计”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X77" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8191,7 +8191,7 @@
         <x:v>product:zhiwei,level:story,release:p3,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC77" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD77" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8263,7 +8263,7 @@
       </x:c>
       <x:c r="V78" s="92"/>
       <x:c r="W78" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>计划评测/权限/工具集成测试：Planner 生成受约束任务图；检查“计划无循环”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X78" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8281,7 +8281,7 @@
         <x:v>product:zhiwei,level:story,release:p3,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC78" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD78" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8353,7 +8353,7 @@
       </x:c>
       <x:c r="V79" s="92"/>
       <x:c r="W79" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>计划评测/权限/工具集成测试：计划人工审阅与修改；检查“修改后重新校验权限与依赖”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X79" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8371,7 +8371,7 @@
         <x:v>product:zhiwei,level:story,release:p3,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC79" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD79" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8441,7 +8441,7 @@
       </x:c>
       <x:c r="V80" s="92"/>
       <x:c r="W80" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>安全策略/越权/审计测试：端到端身份透传与工具侧鉴权；检查“OIDC→会话→JWT→Agent→MCP→数据层身份不断链”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X80" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8459,7 +8459,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC80" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §5 用户与权限</x:v>
       </x:c>
       <x:c r="AD80" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8531,7 +8531,7 @@
       </x:c>
       <x:c r="V81" s="92"/>
       <x:c r="W81" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>安全策略/越权/审计测试：角色与儿童策略；检查“kid 请求强制经过 Compliance”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X81" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8549,7 +8549,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC81" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §5 用户与权限</x:v>
       </x:c>
       <x:c r="AD81" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8593,7 +8593,7 @@
         <x:v>作为家庭成员，我在重启路由器或断开关键插座前能看到影响并明确确认。</x:v>
       </x:c>
       <x:c r="M82" s="92" t="str">
-        <x:v>准备阶段返回影响范围和确认令牌；令牌短期有效且绑定参数；执行与确认人都被审计。</x:v>
+        <x:v>准备阶段返回影响范围和确认令牌；令牌短期有效且绑定参数；执行与确认人都被审计；100% 高风险动作在执行前完成明确确认，确认令牌绑定动作参数。</x:v>
       </x:c>
       <x:c r="N82" s="92" t="str">
         <x:v>不包含未写入验收标准的扩展能力。</x:v>
@@ -8621,7 +8621,7 @@
       </x:c>
       <x:c r="V82" s="92"/>
       <x:c r="W82" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>安全策略/越权/审计测试：高风险动作 prepare/confirm/execute；检查“准备阶段返回影响范围和确认令牌”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X82" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8639,7 +8639,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC82" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §5 用户与权限</x:v>
       </x:c>
       <x:c r="AD82" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8711,7 +8711,7 @@
       </x:c>
       <x:c r="V83" s="92"/>
       <x:c r="W83" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>安全策略/越权/审计测试：不可变审计查询；检查“审计事件追加写”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X83" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8729,7 +8729,7 @@
         <x:v>product:zhiwei,level:story,release:p4,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC83" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §5 用户与权限</x:v>
       </x:c>
       <x:c r="AD83" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8801,7 +8801,7 @@
       </x:c>
       <x:c r="V84" s="92"/>
       <x:c r="W84" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>部署/升级/回滚/恢复演练：全链路 trace 关联；检查“各层共享 trace_id”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X84" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8819,7 +8819,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC84" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD84" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8891,7 +8891,7 @@
       </x:c>
       <x:c r="V85" s="92"/>
       <x:c r="W85" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>部署/升级/回滚/恢复演练：模型用量与预算面板；检查“每个指标显示来源、时间和不可用状态”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X85" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8909,7 +8909,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC85" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD85" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -8981,7 +8981,7 @@
       </x:c>
       <x:c r="V86" s="92"/>
       <x:c r="W86" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>部署/升级/回滚/恢复演练：家庭基础设施健康面板；检查“指标带时间窗”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X86" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -8999,7 +8999,7 @@
         <x:v>product:zhiwei,level:story,release:p3,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC86" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD86" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9069,7 +9069,7 @@
       </x:c>
       <x:c r="V87" s="92"/>
       <x:c r="W87" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>需求门禁/导入/追溯回归：稳定需求 ID 与父子关系；检查“Roadmap、Epic、Story、Task ID 唯一”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X87" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -9087,7 +9087,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC87" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §15 需求与交付追溯</x:v>
       </x:c>
       <x:c r="AD87" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9159,7 +9159,7 @@
       </x:c>
       <x:c r="V88" s="92"/>
       <x:c r="W88" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>需求门禁/导入/追溯回归：Story 结构化契约；检查“必填字段有数据字典与枚举”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X88" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -9177,7 +9177,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC88" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §15 需求与交付追溯</x:v>
       </x:c>
       <x:c r="AD88" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9221,7 +9221,7 @@
         <x:v>作为维护者，我能从 Story 找到架构决策、测试、缺陷、代码和发布。</x:v>
       </x:c>
       <x:c r="M89" s="92" t="str">
-        <x:v>PR 必须引用 Story；架构变化必须引用 ADR；Done 前测试证据齐全且阻塞缺陷关闭。</x:v>
+        <x:v>PR 必须引用 Story；架构变化必须引用 ADR；Done 前测试证据齐全且阻塞缺陷关闭；100% 发布变更可回溯到 Story、测试证据、PR、版本和运行 trace。</x:v>
       </x:c>
       <x:c r="N89" s="92" t="str">
         <x:v>不包含未写入验收标准的扩展能力。</x:v>
@@ -9249,7 +9249,7 @@
       </x:c>
       <x:c r="V89" s="92"/>
       <x:c r="W89" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>需求门禁/导入/追溯回归：ADR/TC/BUG/PR/Release 追溯门禁；检查“PR 必须引用 Story”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X89" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -9267,7 +9267,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC89" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §15 需求与交付追溯</x:v>
       </x:c>
       <x:c r="AD89" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9339,7 +9339,7 @@
       </x:c>
       <x:c r="V90" s="92"/>
       <x:c r="W90" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>需求门禁/导入/追溯回归：Jira 与 GitHub 可移植导入视图；检查“Jira Standard、Jira Advanced 和 GitHub 视图保留逻辑 ID”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X90" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -9357,7 +9357,7 @@
         <x:v>product:zhiwei,level:story,release:p0,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC90" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §15 需求与交付追溯</x:v>
       </x:c>
       <x:c r="AD90" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9429,7 +9429,7 @@
       </x:c>
       <x:c r="V91" s="92"/>
       <x:c r="W91" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>部署/升级/回滚/恢复演练：NAS 容器化部署；检查“部署不依赖开发机”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X91" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -9447,7 +9447,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC91" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD91" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9519,7 +9519,7 @@
       </x:c>
       <x:c r="V92" s="92"/>
       <x:c r="W92" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>部署/升级/回滚/恢复演练：安全升级与回滚；检查“发布前备份”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X92" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -9537,7 +9537,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC92" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD92" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9609,7 +9609,7 @@
       </x:c>
       <x:c r="V93" s="92"/>
       <x:c r="W93" s="92" t="str">
-        <x:v>自动化测试 + 原型或真实设备验收</x:v>
+        <x:v>部署/升级/回滚/恢复演练：局域网降级与灾难恢复；检查“核心控制不依赖公网”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="X93" s="92" t="str">
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
@@ -9627,7 +9627,7 @@
         <x:v>product:zhiwei,level:story,release:p1,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC93" s="91" t="str">
-        <x:v>ZW-PRD-001</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD93" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9711,7 +9711,7 @@
         <x:v>product:zhiwei,level:task,release:p0,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC94" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD94" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9795,7 +9795,7 @@
         <x:v>product:zhiwei,level:task,release:p0,roadmap:zw-rm-01</x:v>
       </x:c>
       <x:c r="AC95" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §9 空间、设备与能力模型</x:v>
       </x:c>
       <x:c r="AD95" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9881,7 +9881,7 @@
         <x:v>product:zhiwei,level:task,release:p1,roadmap:zw-rm-02</x:v>
       </x:c>
       <x:c r="AC96" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §8 设备交互规范</x:v>
       </x:c>
       <x:c r="AD96" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -9965,7 +9965,7 @@
         <x:v>product:zhiwei,level:task,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC97" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §7.4 任务队列</x:v>
       </x:c>
       <x:c r="AD97" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -10049,7 +10049,7 @@
         <x:v>product:zhiwei,level:task,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC98" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §7.4 任务队列</x:v>
       </x:c>
       <x:c r="AD98" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -10133,7 +10133,7 @@
         <x:v>product:zhiwei,level:task,release:p1,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC99" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD99" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -10217,7 +10217,7 @@
         <x:v>product:zhiwei,level:task,release:p3,roadmap:zw-rm-04</x:v>
       </x:c>
       <x:c r="AC100" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §10 系统边界</x:v>
       </x:c>
       <x:c r="AD100" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -10301,7 +10301,7 @@
         <x:v>product:zhiwei,level:task,release:p0,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC101" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §5 用户与权限</x:v>
       </x:c>
       <x:c r="AD101" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -10385,7 +10385,7 @@
         <x:v>product:zhiwei,level:task,release:p1,roadmap:zw-rm-05</x:v>
       </x:c>
       <x:c r="AC102" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD102" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -10469,7 +10469,7 @@
         <x:v>product:zhiwei,level:task,release:p0,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC103" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §15 需求与交付追溯</x:v>
       </x:c>
       <x:c r="AD103" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -10553,7 +10553,7 @@
         <x:v>product:zhiwei,level:task,release:p1,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC104" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD104" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -10637,7 +10637,7 @@
         <x:v>product:zhiwei,level:task,release:p1,roadmap:zw-rm-06</x:v>
       </x:c>
       <x:c r="AC105" s="91" t="str">
-        <x:v>父 Story</x:v>
+        <x:v>ZW-PRD-001 §11 非功能需求</x:v>
       </x:c>
       <x:c r="AD105" s="94" t="str">
         <x:v>2026-09-27</x:v>
@@ -10667,7 +10667,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea65664cdef4423c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5a17bbfb6db44f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10735,7 +10735,7 @@
         <x:v>Status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="198" hidden="0" customHeight="1">
       <x:c r="A2" s="91" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -10781,7 +10781,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="198" hidden="0" customHeight="1">
       <x:c r="A3" s="91" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -10827,7 +10827,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="198" hidden="0" customHeight="1">
       <x:c r="A4" s="91" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -10873,7 +10873,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="198" hidden="0" customHeight="1">
       <x:c r="A5" s="91" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -10919,7 +10919,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="198" hidden="0" customHeight="1">
       <x:c r="A6" s="91" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -10965,7 +10965,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="198" hidden="0" customHeight="1">
       <x:c r="A7" s="91" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -11011,7 +11011,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="198" hidden="0" customHeight="1">
       <x:c r="A8" s="91" t="n">
         <x:v>13</x:v>
       </x:c>
@@ -11057,7 +11057,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="198" hidden="0" customHeight="1">
       <x:c r="A9" s="91" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -11103,7 +11103,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="198" hidden="0" customHeight="1">
       <x:c r="A10" s="91" t="n">
         <x:v>15</x:v>
       </x:c>
@@ -11149,7 +11149,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="198" hidden="0" customHeight="1">
       <x:c r="A11" s="91" t="n">
         <x:v>16</x:v>
       </x:c>
@@ -11195,7 +11195,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="198" hidden="0" customHeight="1">
       <x:c r="A12" s="91" t="n">
         <x:v>17</x:v>
       </x:c>
@@ -11241,7 +11241,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="198" hidden="0" customHeight="1">
       <x:c r="A13" s="91" t="n">
         <x:v>18</x:v>
       </x:c>
@@ -11287,7 +11287,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="198" hidden="0" customHeight="1">
       <x:c r="A14" s="91" t="n">
         <x:v>19</x:v>
       </x:c>
@@ -11333,7 +11333,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="198" hidden="0" customHeight="1">
       <x:c r="A15" s="91" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -11379,7 +11379,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="198" hidden="0" customHeight="1">
       <x:c r="A16" s="91" t="n">
         <x:v>21</x:v>
       </x:c>
@@ -11425,7 +11425,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="198" hidden="0" customHeight="1">
       <x:c r="A17" s="91" t="n">
         <x:v>22</x:v>
       </x:c>
@@ -11471,7 +11471,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="198" hidden="0" customHeight="1">
       <x:c r="A18" s="91" t="n">
         <x:v>23</x:v>
       </x:c>
@@ -11517,7 +11517,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="198" hidden="0" customHeight="1">
       <x:c r="A19" s="91" t="n">
         <x:v>24</x:v>
       </x:c>
@@ -11563,7 +11563,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="264" hidden="0" customHeight="1">
       <x:c r="A20" s="91" t="n">
         <x:v>25</x:v>
       </x:c>
@@ -11583,7 +11583,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：建立多建筑多楼层空间树；检查“可创建、重命名、排序和停用空间节点”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E20" s="91" t="n">
         <x:v>7</x:v>
@@ -11613,7 +11613,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
+    <x:row r="21" ht="264" hidden="0" customHeight="1">
       <x:c r="A21" s="91" t="n">
         <x:v>26</x:v>
       </x:c>
@@ -11633,7 +11633,7 @@
 Dependencies
 - ZW-ST-0201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：按 Device Profile 添加设备；检查“向导依次完成模板选择、命名、参数、空间归属和连接验证”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E21" s="91" t="n">
         <x:v>7</x:v>
@@ -11663,7 +11663,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A22" s="91" t="n">
         <x:v>27</x:v>
       </x:c>
@@ -11683,7 +11683,7 @@
 Dependencies
 - ZW-ST-0101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：编辑设备参数与空间归属；检查“保存后 device_id 不变”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E22" s="91" t="n">
         <x:v>7</x:v>
@@ -11713,7 +11713,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
+    <x:row r="23" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A23" s="91" t="n">
         <x:v>28</x:v>
       </x:c>
@@ -11733,7 +11733,7 @@
 Dependencies
 - ZW-ST-0102
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：设备详情渐进披露；检查“详情页展示状态、能力、任务历史和适配器信息”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E23" s="91" t="n">
         <x:v>7</x:v>
@@ -11763,7 +11763,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A24" s="91" t="n">
         <x:v>29</x:v>
       </x:c>
@@ -11783,7 +11783,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：定义 Device Profile v0 契约；检查“Schema 覆盖本 PRD 的 12 类交互”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E24" s="91" t="n">
         <x:v>8</x:v>
@@ -11813,7 +11813,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
+    <x:row r="25" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A25" s="91" t="n">
         <x:v>30</x:v>
       </x:c>
@@ -11833,7 +11833,7 @@
 Dependencies
 - ZW-ST-0201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：注册设备能力并供 UI 查询；检查“API 返回 capability_id、动作、参数、权限、风险和状态 Schema”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E25" s="91" t="n">
         <x:v>8</x:v>
@@ -11863,7 +11863,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
+    <x:row r="26" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A26" s="91" t="n">
         <x:v>31</x:v>
       </x:c>
@@ -11883,7 +11883,7 @@
 Dependencies
 - ZW-ST-0201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：建立家庭 Ontology v0；检查“Ontology 有版本和迁移记录”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E26" s="91" t="n">
         <x:v>8</x:v>
@@ -11913,7 +11913,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
+    <x:row r="27" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A27" s="91" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -11933,7 +11933,7 @@
 Dependencies
 - ZW-ST-0201,ZW-ST-0203
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：能力 Schema 兼容迁移；检查“升级前给出兼容性检查”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E27" s="91" t="n">
         <x:v>8</x:v>
@@ -11963,7 +11963,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
+    <x:row r="28" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A28" s="91" t="n">
         <x:v>33</x:v>
       </x:c>
@@ -11977,13 +11977,13 @@
         <x:v>Logical ID: ZW-ST-0301
 作为家庭成员，我打开首页时能看到设备状态和状态时间。
 Acceptance Criteria
-- 局域网目标 2 秒内返回快照；每个状态含 observed_at 和 freshness；不可用值显示未知而非 0。
+- 局域网目标 2 秒内返回快照；每个状态含 observed_at 和 freshness；不可用值显示未知而非 0；在目标环境采样中，95% 在线设备状态在定义的心跳窗口内更新。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：读取家庭状态快照；检查“局域网目标 2 秒内返回快照”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E28" s="91" t="n">
         <x:v>9</x:v>
@@ -12013,7 +12013,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
+    <x:row r="29" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A29" s="91" t="n">
         <x:v>34</x:v>
       </x:c>
@@ -12033,7 +12033,7 @@
 Dependencies
 - ZW-ST-0301,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：订阅设备与任务事件；检查“SSE 或等价事件流支持断线重连和游标续传”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E29" s="91" t="n">
         <x:v>9</x:v>
@@ -12063,7 +12063,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
+    <x:row r="30" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A30" s="91" t="n">
         <x:v>35</x:v>
       </x:c>
@@ -12083,7 +12083,7 @@
 Dependencies
 - ZW-ST-0301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：离线设备浅灰遮罩；检查“离线判定使用心跳窗口”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E30" s="91" t="n">
         <x:v>9</x:v>
@@ -12113,7 +12113,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
+    <x:row r="31" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A31" s="91" t="n">
         <x:v>36</x:v>
       </x:c>
@@ -12127,13 +12127,13 @@
         <x:v>Logical ID: ZW-ST-0304
 作为家庭成员，我能分辨系统正在尝试的状态和设备已确认的状态。
 Acceptance Criteria
-- 任务运行时展示 pending/running；只在设备上报或回查成功后更新 confirmed state；超时显示不确定。
+- 任务运行时展示 pending/running；只在设备上报或回查成功后更新 confirmed state；超时显示不确定；任务“成功”与设备真实状态一致率 ≥ 99%。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-0302
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：区分期望状态与确认状态；检查“任务运行时展示 pending/running”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E31" s="91" t="n">
         <x:v>9</x:v>
@@ -12163,7 +12163,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A32" s="91" t="n">
         <x:v>37</x:v>
       </x:c>
@@ -12183,7 +12183,7 @@
 Dependencies
 - ZW-ST-0101,ZW-ST-0301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：展示家庭网络拓扑；检查“拓扑支持父子链路、连接类型和节点状态”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E32" s="91" t="n">
         <x:v>10</x:v>
@@ -12213,7 +12213,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
+    <x:row r="33" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A33" s="91" t="n">
         <x:v>38</x:v>
       </x:c>
@@ -12233,7 +12233,7 @@
 Dependencies
 - ZW-ST-0401
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：查看网络节点健康度；检查“节点详情字段来源明确”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E33" s="91" t="n">
         <x:v>10</x:v>
@@ -12263,7 +12263,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
+    <x:row r="34" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A34" s="91" t="n">
         <x:v>39</x:v>
       </x:c>
@@ -12283,7 +12283,7 @@
 Dependencies
 - ZW-ST-0401
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：从拓扑进入设备详情；检查“有关联 device_id 的节点可打开设备详情”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E34" s="91" t="n">
         <x:v>10</x:v>
@@ -12313,7 +12313,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
+    <x:row r="35" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A35" s="91" t="n">
         <x:v>40</x:v>
       </x:c>
@@ -12327,13 +12327,13 @@
         <x:v>Logical ID: ZW-ST-0501
 作为家庭成员，我能按房间扫描所有关键设备和状态。
 Acceptance Criteria
-- 卡片按建筑/楼层/房间稳定排序；房间标题显示聚合状态；未归属设备进入待整理分组。
+- 卡片按建筑/楼层/房间稳定排序；房间标题显示聚合状态；未归属设备进入待整理分组；80% 的常用动作可在首页两次交互内完成。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-0101,ZW-ST-0301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：按房间归类首页卡片；检查“卡片按建筑/楼层/房间稳定排序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E35" s="91" t="n">
         <x:v>11</x:v>
@@ -12363,7 +12363,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
+    <x:row r="36" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A36" s="91" t="n">
         <x:v>41</x:v>
       </x:c>
@@ -12383,7 +12383,7 @@
 Dependencies
 - ZW-ST-0501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：有限尺寸 Widget 网格；检查“仅允许预定义尺寸”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E36" s="91" t="n">
         <x:v>11</x:v>
@@ -12413,7 +12413,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
+    <x:row r="37" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A37" s="91" t="n">
         <x:v>42</x:v>
       </x:c>
@@ -12433,7 +12433,7 @@
 Dependencies
 - ZW-ST-0501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：卡片与户型图二级视图；检查“默认进入卡片视图”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E37" s="91" t="n">
         <x:v>11</x:v>
@@ -12463,7 +12463,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
+    <x:row r="38" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A38" s="91" t="n">
         <x:v>43</x:v>
       </x:c>
@@ -12483,7 +12483,7 @@
 Dependencies
 - ZW-ST-0202,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：空调温度步进控件；检查“控件显示允许范围”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E38" s="91" t="n">
         <x:v>12</x:v>
@@ -12513,7 +12513,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
+    <x:row r="39" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A39" s="91" t="n">
         <x:v>44</x:v>
       </x:c>
@@ -12533,7 +12533,7 @@
 Dependencies
 - ZW-ST-0202,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：可调灯开关与亮度滑条；检查“开关关闭时滑条隐藏”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E39" s="91" t="n">
         <x:v>12</x:v>
@@ -12563,7 +12563,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
+    <x:row r="40" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A40" s="91" t="n">
         <x:v>45</x:v>
       </x:c>
@@ -12583,7 +12583,7 @@
 Dependencies
 - ZW-ST-1202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：对开窗帘开停关交互；检查“打开完成显示 0%，关闭完成显示 100%”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E40" s="91" t="n">
         <x:v>12</x:v>
@@ -12613,7 +12613,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
+    <x:row r="41" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A41" s="91" t="n">
         <x:v>46</x:v>
       </x:c>
@@ -12633,7 +12633,7 @@
 Dependencies
 - ZW-ST-1202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：卷帘开停关交互；检查“开为 0%、关为 100%”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E41" s="91" t="n">
         <x:v>12</x:v>
@@ -12663,7 +12663,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
+    <x:row r="42" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A42" s="91" t="n">
         <x:v>47</x:v>
       </x:c>
@@ -12683,7 +12683,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：鱼缸灯光与投食交互；检查“投食期间按钮显示旋转状态且不可重复提交”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E42" s="91" t="n">
         <x:v>12</x:v>
@@ -12713,7 +12713,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
+    <x:row r="43" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A43" s="91" t="n">
         <x:v>48</x:v>
       </x:c>
@@ -12733,7 +12733,7 @@
 Dependencies
 - ZW-ST-1503
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：智能插座与用电统计；检查“统计口径和更新时间可见”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E43" s="91" t="n">
         <x:v>12</x:v>
@@ -12763,7 +12763,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
+    <x:row r="44" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A44" s="91" t="n">
         <x:v>49</x:v>
       </x:c>
@@ -12783,7 +12783,7 @@
 Dependencies
 - ZW-ST-1503,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：路由器安全重启；检查“点击后显示影响范围与预计离线时间”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E44" s="91" t="n">
         <x:v>12</x:v>
@@ -12813,7 +12813,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="45">
+    <x:row r="45" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A45" s="91" t="n">
         <x:v>50</x:v>
       </x:c>
@@ -12833,7 +12833,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：扫地机器人全屋清洁快捷操作；检查“首页仅有全屋清洁”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E45" s="91" t="n">
         <x:v>12</x:v>
@@ -12863,7 +12863,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
+    <x:row r="46" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A46" s="91" t="n">
         <x:v>51</x:v>
       </x:c>
@@ -12883,7 +12883,7 @@
 Dependencies
 - ZW-ST-1502
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：长按语音设备指令；检查“界面明确提示按住说话”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E46" s="91" t="n">
         <x:v>12</x:v>
@@ -12913,7 +12913,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="47">
+    <x:row r="47" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A47" s="91" t="n">
         <x:v>52</x:v>
       </x:c>
@@ -12933,7 +12933,7 @@
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：个人电子设备只读状态；检查“卡片仅展示在线、网络和最后心跳”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E47" s="91" t="n">
         <x:v>12</x:v>
@@ -12963,7 +12963,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="48">
+    <x:row r="48" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A48" s="91" t="n">
         <x:v>53</x:v>
       </x:c>
@@ -12983,7 +12983,7 @@
 Dependencies
 - ZW-ST-1602
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：中枢额度与数据中心指标卡；检查“额度显示 5 小时、周限额和预充值余额及更新时间”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E48" s="91" t="n">
         <x:v>12</x:v>
@@ -13013,7 +13013,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
+    <x:row r="49" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A49" s="91" t="n">
         <x:v>54</x:v>
       </x:c>
@@ -13033,7 +13033,7 @@
 Dependencies
 - ZW-ST-0501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：四档响应式网格；检查“折叠外屏压缩为单列重点信息”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E49" s="91" t="n">
         <x:v>13</x:v>
@@ -13063,7 +13063,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="50">
+    <x:row r="50" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A50" s="91" t="n">
         <x:v>55</x:v>
       </x:c>
@@ -13083,7 +13083,7 @@
 Dependencies
 - ZW-ST-0701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：无限信息流与侧边栏版权；检查“主内容自然滚动”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E50" s="91" t="n">
         <x:v>13</x:v>
@@ -13113,7 +13113,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="51">
+    <x:row r="51" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A51" s="91" t="n">
         <x:v>56</x:v>
       </x:c>
@@ -13133,7 +13133,7 @@
 Dependencies
 - ZW-ST-0701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：键盘、读屏与减少动态效果；检查“控件有可访问名称和焦点顺序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E51" s="91" t="n">
         <x:v>13</x:v>
@@ -13163,7 +13163,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="52">
+    <x:row r="52" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A52" s="91" t="n">
         <x:v>57</x:v>
       </x:c>
@@ -13183,7 +13183,7 @@
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：添加单设备动作卡；检查“只能选择设备已注册的动作”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E52" s="91" t="n">
         <x:v>14</x:v>
@@ -13213,7 +13213,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
+    <x:row r="53" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A53" s="91" t="n">
         <x:v>58</x:v>
       </x:c>
@@ -13233,7 +13233,7 @@
 Dependencies
 - ZW-ST-0801
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：在一张卡中组合并行动作；检查“同卡动作无依赖时并行执行”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E53" s="91" t="n">
         <x:v>14</x:v>
@@ -13263,7 +13263,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="54">
+    <x:row r="54" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A54" s="91" t="n">
         <x:v>59</x:v>
       </x:c>
@@ -13283,7 +13283,7 @@
 Dependencies
 - ZW-ST-0802
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：步骤排序与依赖校验；检查“支持拖动和键盘排序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E54" s="91" t="n">
         <x:v>14</x:v>
@@ -13313,7 +13313,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="55">
+    <x:row r="55" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A55" s="91" t="n">
         <x:v>60</x:v>
       </x:c>
@@ -13333,7 +13333,7 @@
 Dependencies
 - ZW-ST-0803
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：场景草稿、Review 与发布；检查“草稿和已发布版本分离”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E55" s="91" t="n">
         <x:v>14</x:v>
@@ -13363,7 +13363,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="56">
+    <x:row r="56" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A56" s="91" t="n">
         <x:v>61</x:v>
       </x:c>
@@ -13383,7 +13383,7 @@
 Dependencies
 - ZW-ST-0804,ZW-ST-1101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 场景走查/指标验收：观影模式预置场景；检查“包含窗帘、灯、电视、Apple TV/Infuse、NAS 推荐和语音播报”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E56" s="91" t="n">
         <x:v>15</x:v>
@@ -13413,7 +13413,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="57">
+    <x:row r="57" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A57" s="91" t="n">
         <x:v>62</x:v>
       </x:c>
@@ -13433,7 +13433,7 @@
 Dependencies
 - ZW-ST-0804,ZW-ST-1101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 场景走查/指标验收：离家模式预置场景；检查“按能力发现目标而非写死设备清单”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E57" s="91" t="n">
         <x:v>15</x:v>
@@ -13463,7 +13463,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="58">
+    <x:row r="58" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A58" s="91" t="n">
         <x:v>63</x:v>
       </x:c>
@@ -13483,7 +13483,7 @@
 Dependencies
 - ZW-ST-1401,ZW-ST-0801
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：自然语言生成场景草稿；检查“系统展示解析出的意图、设备、动作和假设”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E58" s="91" t="n">
         <x:v>16</x:v>
@@ -13513,7 +13513,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="59">
+    <x:row r="59" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A59" s="91" t="n">
         <x:v>64</x:v>
       </x:c>
@@ -13533,7 +13533,7 @@
 Dependencies
 - ZW-ST-1402
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：Skill 匹配与 Plan Mode 分流；检查“路由结果含匹配依据和置信度”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E59" s="91" t="n">
         <x:v>16</x:v>
@@ -13563,7 +13563,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="60">
+    <x:row r="60" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A60" s="91" t="n">
         <x:v>65</x:v>
       </x:c>
@@ -13583,7 +13583,7 @@
 Dependencies
 - ZW-ST-1303,ZW-ST-1103
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：下载电影长程工作流；检查“计划调用 NAS 搜索 MCP、过滤候选、下载 MCP、等待完成和微信通知”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E60" s="91" t="n">
         <x:v>16</x:v>
@@ -13613,7 +13613,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="61">
+    <x:row r="61" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A61" s="91" t="n">
         <x:v>66</x:v>
       </x:c>
@@ -13627,13 +13627,13 @@
         <x:v>Logical ID: ZW-ST-1101
 作为家庭成员，我触发场景后能看到每张卡和卡内动作的实时状态。
 Acceptance Criteria
-- 状态包含等待、运行、成功、失败、跳过和待确认；页面刷新后能恢复同一运行实例。
+- 状态包含等待、运行、成功、失败、跳过和待确认；页面刷新后能恢复同一运行实例；已发布场景完整执行成功率 ≥ 95%，失败步骤可定位。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-1201,ZW-ST-0302
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：逐卡执行并展示结果；检查“状态包含等待、运行、成功、失败、跳过和待确认”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E61" s="91" t="n">
         <x:v>17</x:v>
@@ -13663,7 +13663,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="62">
+    <x:row r="62" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A62" s="91" t="n">
         <x:v>67</x:v>
       </x:c>
@@ -13683,7 +13683,7 @@
 Dependencies
 - ZW-ST-1101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：失败策略、重试与取消；检查“错误码映射为可行动说明”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E62" s="91" t="n">
         <x:v>17</x:v>
@@ -13713,7 +13713,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="63">
+    <x:row r="63" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A63" s="91" t="n">
         <x:v>68</x:v>
       </x:c>
@@ -13733,7 +13733,7 @@
 Dependencies
 - ZW-ST-1203
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：长程流程断点续跑；检查“关键节点写入 checkpointer”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E63" s="91" t="n">
         <x:v>17</x:v>
@@ -13763,7 +13763,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="64">
+    <x:row r="64" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A64" s="91" t="n">
         <x:v>69</x:v>
       </x:c>
@@ -13783,7 +13783,7 @@
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：统一异步任务契约；检查“任务含 idempotency_key、发起者、目标、参数、风险、超时、重试、trace_id 和标准状态机”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E64" s="91" t="n">
         <x:v>18</x:v>
@@ -13813,7 +13813,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="65">
+    <x:row r="65" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A65" s="91" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -13833,7 +13833,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：优先队列强制状态上报；检查“优先队列拒绝同步任务”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E65" s="91" t="n">
         <x:v>18</x:v>
@@ -13863,7 +13863,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="66">
+    <x:row r="66" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A66" s="91" t="n">
         <x:v>71</x:v>
       </x:c>
@@ -13883,7 +13883,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：超时、重试和死信恢复；检查“重试次数与退避可配置”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E66" s="91" t="n">
         <x:v>18</x:v>
@@ -13913,7 +13913,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="67">
+    <x:row r="67" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A67" s="91" t="n">
         <x:v>72</x:v>
       </x:c>
@@ -13933,7 +13933,7 @@
 Dependencies
 - ZW-ST-1202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：任务队列双视图；检查“两类队列可筛选”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E67" s="91" t="n">
         <x:v>18</x:v>
@@ -13963,7 +13963,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="68">
+    <x:row r="68" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A68" s="91" t="n">
         <x:v>73</x:v>
       </x:c>
@@ -13983,7 +13983,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：MCP 工具发现与能力白名单；检查“网关按身份、角色、设备和风险返回白名单”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E68" s="91" t="n">
         <x:v>19</x:v>
@@ -14013,7 +14013,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="69">
+    <x:row r="69" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A69" s="91" t="n">
         <x:v>74</x:v>
       </x:c>
@@ -14033,7 +14033,7 @@
 Dependencies
 - ZW-ST-0201,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：设备适配器标准接口；检查“接口有契约测试”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E69" s="91" t="n">
         <x:v>19</x:v>
@@ -14063,7 +14063,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="70">
+    <x:row r="70" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A70" s="91" t="n">
         <x:v>75</x:v>
       </x:c>
@@ -14083,7 +14083,7 @@
 Dependencies
 - ZW-ST-1302
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：首批真实服务与设备接入；检查“至少 5 类真实接入通过读写/只读能力声明”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E70" s="91" t="n">
         <x:v>19</x:v>
@@ -14113,7 +14113,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
+    <x:row r="71" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A71" s="91" t="n">
         <x:v>76</x:v>
       </x:c>
@@ -14133,7 +14133,7 @@
 Dependencies
 - ZW-ST-1503
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：意图与风险分级；检查“分类结果可解释且进入审计”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E71" s="91" t="n">
         <x:v>20</x:v>
@@ -14163,7 +14163,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="72">
+    <x:row r="72" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A72" s="91" t="n">
         <x:v>77</x:v>
       </x:c>
@@ -14183,7 +14183,7 @@
 Dependencies
 - ZW-ST-1401,ZW-ST-1301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：Planner 生成受约束任务图；检查“计划无循环”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E72" s="91" t="n">
         <x:v>20</x:v>
@@ -14213,7 +14213,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="73">
+    <x:row r="73" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A73" s="91" t="n">
         <x:v>78</x:v>
       </x:c>
@@ -14233,7 +14233,7 @@
 Dependencies
 - ZW-ST-1402
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：计划人工审阅与修改；检查“修改后重新校验权限与依赖”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E73" s="91" t="n">
         <x:v>20</x:v>
@@ -14263,7 +14263,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="74">
+    <x:row r="74" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A74" s="91" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -14283,7 +14283,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：端到端身份透传与工具侧鉴权；检查“OIDC→会话→JWT→Agent→MCP→数据层身份不断链”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E74" s="91" t="n">
         <x:v>21</x:v>
@@ -14313,7 +14313,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="75">
+    <x:row r="75" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A75" s="91" t="n">
         <x:v>80</x:v>
       </x:c>
@@ -14333,7 +14333,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：角色与儿童策略；检查“kid 请求强制经过 Compliance”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E75" s="91" t="n">
         <x:v>21</x:v>
@@ -14363,7 +14363,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="76">
+    <x:row r="76" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A76" s="91" t="n">
         <x:v>81</x:v>
       </x:c>
@@ -14377,13 +14377,13 @@
         <x:v>Logical ID: ZW-ST-1503
 作为家庭成员，我在重启路由器或断开关键插座前能看到影响并明确确认。
 Acceptance Criteria
-- 准备阶段返回影响范围和确认令牌；令牌短期有效且绑定参数；执行与确认人都被审计。
+- 准备阶段返回影响范围和确认令牌；令牌短期有效且绑定参数；执行与确认人都被审计；100% 高风险动作在执行前完成明确确认，确认令牌绑定动作参数。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：高风险动作 prepare/confirm/execute；检查“准备阶段返回影响范围和确认令牌”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E76" s="91" t="n">
         <x:v>21</x:v>
@@ -14413,7 +14413,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="77">
+    <x:row r="77" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A77" s="91" t="n">
         <x:v>82</x:v>
       </x:c>
@@ -14433,7 +14433,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：不可变审计查询；检查“审计事件追加写”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E77" s="91" t="n">
         <x:v>21</x:v>
@@ -14463,7 +14463,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="78">
+    <x:row r="78" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A78" s="91" t="n">
         <x:v>83</x:v>
       </x:c>
@@ -14483,7 +14483,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：全链路 trace 关联；检查“各层共享 trace_id”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E78" s="91" t="n">
         <x:v>22</x:v>
@@ -14513,7 +14513,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="79">
+    <x:row r="79" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A79" s="91" t="n">
         <x:v>84</x:v>
       </x:c>
@@ -14533,7 +14533,7 @@
 Dependencies
 - ZW-ST-1601
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：模型用量与预算面板；检查“每个指标显示来源、时间和不可用状态”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E79" s="91" t="n">
         <x:v>22</x:v>
@@ -14563,7 +14563,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="80">
+    <x:row r="80" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A80" s="91" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -14583,7 +14583,7 @@
 Dependencies
 - ZW-ST-1601
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：家庭基础设施健康面板；检查“指标带时间窗”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E80" s="91" t="n">
         <x:v>22</x:v>
@@ -14613,7 +14613,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="81">
+    <x:row r="81" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A81" s="91" t="n">
         <x:v>86</x:v>
       </x:c>
@@ -14633,7 +14633,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：稳定需求 ID 与父子关系；检查“Roadmap、Epic、Story、Task ID 唯一”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E81" s="91" t="n">
         <x:v>23</x:v>
@@ -14663,7 +14663,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="82">
+    <x:row r="82" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A82" s="91" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -14683,7 +14683,7 @@
 Dependencies
 - ZW-ST-1701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：Story 结构化契约；检查“必填字段有数据字典与枚举”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E82" s="91" t="n">
         <x:v>23</x:v>
@@ -14713,7 +14713,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="83">
+    <x:row r="83" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A83" s="91" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -14727,13 +14727,13 @@
         <x:v>Logical ID: ZW-ST-1703
 作为维护者，我能从 Story 找到架构决策、测试、缺陷、代码和发布。
 Acceptance Criteria
-- PR 必须引用 Story；架构变化必须引用 ADR；Done 前测试证据齐全且阻塞缺陷关闭。
+- PR 必须引用 Story；架构变化必须引用 ADR；Done 前测试证据齐全且阻塞缺陷关闭；100% 发布变更可回溯到 Story、测试证据、PR、版本和运行 trace。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-1702
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：ADR/TC/BUG/PR/Release 追溯门禁；检查“PR 必须引用 Story”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E83" s="91" t="n">
         <x:v>23</x:v>
@@ -14763,7 +14763,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="84">
+    <x:row r="84" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A84" s="91" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -14783,7 +14783,7 @@
 Dependencies
 - ZW-ST-1701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：Jira 与 GitHub 可移植导入视图；检查“Jira Standard、Jira Advanced 和 GitHub 视图保留逻辑 ID”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E84" s="91" t="n">
         <x:v>23</x:v>
@@ -14813,7 +14813,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="85">
+    <x:row r="85" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A85" s="91" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -14833,7 +14833,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：NAS 容器化部署；检查“部署不依赖开发机”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E85" s="91" t="n">
         <x:v>24</x:v>
@@ -14863,7 +14863,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="86">
+    <x:row r="86" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A86" s="91" t="n">
         <x:v>91</x:v>
       </x:c>
@@ -14883,7 +14883,7 @@
 Dependencies
 - ZW-ST-1801
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：安全升级与回滚；检查“发布前备份”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E86" s="91" t="n">
         <x:v>24</x:v>
@@ -14913,7 +14913,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="87">
+    <x:row r="87" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A87" s="91" t="n">
         <x:v>92</x:v>
       </x:c>
@@ -14933,7 +14933,7 @@
 Dependencies
 - ZW-ST-1801,ZW-ST-1203
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：局域网降级与灾难恢复；检查“核心控制不依赖公网”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E87" s="91" t="n">
         <x:v>24</x:v>
@@ -14963,7 +14963,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="88">
+    <x:row r="88" ht="198" hidden="0" customHeight="1">
       <x:c r="A88" s="91" t="n">
         <x:v>93</x:v>
       </x:c>
@@ -15011,7 +15011,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="89">
+    <x:row r="89" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A89" s="91" t="n">
         <x:v>94</x:v>
       </x:c>
@@ -15059,7 +15059,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="90">
+    <x:row r="90" ht="198" hidden="0" customHeight="1">
       <x:c r="A90" s="91" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -15107,7 +15107,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="91">
+    <x:row r="91" ht="198" hidden="0" customHeight="1">
       <x:c r="A91" s="91" t="n">
         <x:v>96</x:v>
       </x:c>
@@ -15155,7 +15155,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="92">
+    <x:row r="92" ht="198" hidden="0" customHeight="1">
       <x:c r="A92" s="91" t="n">
         <x:v>97</x:v>
       </x:c>
@@ -15203,7 +15203,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="93">
+    <x:row r="93" ht="198" hidden="0" customHeight="1">
       <x:c r="A93" s="91" t="n">
         <x:v>98</x:v>
       </x:c>
@@ -15251,7 +15251,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="94">
+    <x:row r="94" ht="198" hidden="0" customHeight="1">
       <x:c r="A94" s="91" t="n">
         <x:v>99</x:v>
       </x:c>
@@ -15299,7 +15299,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="95">
+    <x:row r="95" ht="198" hidden="0" customHeight="1">
       <x:c r="A95" s="91" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -15347,7 +15347,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="96">
+    <x:row r="96" ht="198" hidden="0" customHeight="1">
       <x:c r="A96" s="91" t="n">
         <x:v>101</x:v>
       </x:c>
@@ -15395,7 +15395,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="97">
+    <x:row r="97" ht="198" hidden="0" customHeight="1">
       <x:c r="A97" s="91" t="n">
         <x:v>102</x:v>
       </x:c>
@@ -15443,7 +15443,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="98">
+    <x:row r="98" ht="198" hidden="0" customHeight="1">
       <x:c r="A98" s="91" t="n">
         <x:v>103</x:v>
       </x:c>
@@ -15491,7 +15491,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="99">
+    <x:row r="99" ht="198" hidden="0" customHeight="1">
       <x:c r="A99" s="91" t="n">
         <x:v>104</x:v>
       </x:c>
@@ -15542,7 +15542,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2a47df4ab604663"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6577191564954a62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15606,7 +15606,7 @@
         <x:v>Status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="198" hidden="0" customHeight="1">
       <x:c r="A2" s="91" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -15647,7 +15647,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="198" hidden="0" customHeight="1">
       <x:c r="A3" s="91" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -15688,7 +15688,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="198" hidden="0" customHeight="1">
       <x:c r="A4" s="91" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -15729,7 +15729,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="198" hidden="0" customHeight="1">
       <x:c r="A5" s="91" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -15770,7 +15770,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="198" hidden="0" customHeight="1">
       <x:c r="A6" s="91" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -15811,7 +15811,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="198" hidden="0" customHeight="1">
       <x:c r="A7" s="91" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -15852,7 +15852,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="198" hidden="0" customHeight="1">
       <x:c r="A8" s="91" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -15897,7 +15897,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="198" hidden="0" customHeight="1">
       <x:c r="A9" s="91" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -15942,7 +15942,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="198" hidden="0" customHeight="1">
       <x:c r="A10" s="91" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -15987,7 +15987,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="198" hidden="0" customHeight="1">
       <x:c r="A11" s="91" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -16032,7 +16032,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="198" hidden="0" customHeight="1">
       <x:c r="A12" s="91" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -16077,7 +16077,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="198" hidden="0" customHeight="1">
       <x:c r="A13" s="91" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -16122,7 +16122,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="198" hidden="0" customHeight="1">
       <x:c r="A14" s="91" t="n">
         <x:v>13</x:v>
       </x:c>
@@ -16167,7 +16167,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="198" hidden="0" customHeight="1">
       <x:c r="A15" s="91" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -16212,7 +16212,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="198" hidden="0" customHeight="1">
       <x:c r="A16" s="91" t="n">
         <x:v>15</x:v>
       </x:c>
@@ -16257,7 +16257,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="198" hidden="0" customHeight="1">
       <x:c r="A17" s="91" t="n">
         <x:v>16</x:v>
       </x:c>
@@ -16302,7 +16302,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="198" hidden="0" customHeight="1">
       <x:c r="A18" s="91" t="n">
         <x:v>17</x:v>
       </x:c>
@@ -16347,7 +16347,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="198" hidden="0" customHeight="1">
       <x:c r="A19" s="91" t="n">
         <x:v>18</x:v>
       </x:c>
@@ -16392,7 +16392,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="198" hidden="0" customHeight="1">
       <x:c r="A20" s="91" t="n">
         <x:v>19</x:v>
       </x:c>
@@ -16437,7 +16437,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
+    <x:row r="21" ht="198" hidden="0" customHeight="1">
       <x:c r="A21" s="91" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -16482,7 +16482,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="198" hidden="0" customHeight="1">
       <x:c r="A22" s="91" t="n">
         <x:v>21</x:v>
       </x:c>
@@ -16527,7 +16527,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
+    <x:row r="23" ht="198" hidden="0" customHeight="1">
       <x:c r="A23" s="91" t="n">
         <x:v>22</x:v>
       </x:c>
@@ -16572,7 +16572,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="198" hidden="0" customHeight="1">
       <x:c r="A24" s="91" t="n">
         <x:v>23</x:v>
       </x:c>
@@ -16617,7 +16617,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
+    <x:row r="25" ht="198" hidden="0" customHeight="1">
       <x:c r="A25" s="91" t="n">
         <x:v>24</x:v>
       </x:c>
@@ -16662,7 +16662,7 @@
         <x:v>Ready</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
+    <x:row r="26" ht="264" hidden="0" customHeight="1">
       <x:c r="A26" s="91" t="n">
         <x:v>25</x:v>
       </x:c>
@@ -16682,7 +16682,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：建立多建筑多楼层空间树；检查“可创建、重命名、排序和停用空间节点”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E26" s="91" t="n">
         <x:v>7</x:v>
@@ -16709,7 +16709,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
+    <x:row r="27" ht="264" hidden="0" customHeight="1">
       <x:c r="A27" s="91" t="n">
         <x:v>26</x:v>
       </x:c>
@@ -16729,7 +16729,7 @@
 Dependencies
 - ZW-ST-0201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：按 Device Profile 添加设备；检查“向导依次完成模板选择、命名、参数、空间归属和连接验证”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E27" s="91" t="n">
         <x:v>7</x:v>
@@ -16756,7 +16756,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
+    <x:row r="28" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A28" s="91" t="n">
         <x:v>27</x:v>
       </x:c>
@@ -16776,7 +16776,7 @@
 Dependencies
 - ZW-ST-0101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：编辑设备参数与空间归属；检查“保存后 device_id 不变”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E28" s="91" t="n">
         <x:v>7</x:v>
@@ -16803,7 +16803,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
+    <x:row r="29" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A29" s="91" t="n">
         <x:v>28</x:v>
       </x:c>
@@ -16823,7 +16823,7 @@
 Dependencies
 - ZW-ST-0102
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：设备详情渐进披露；检查“详情页展示状态、能力、任务历史和适配器信息”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E29" s="91" t="n">
         <x:v>7</x:v>
@@ -16850,7 +16850,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
+    <x:row r="30" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A30" s="91" t="n">
         <x:v>29</x:v>
       </x:c>
@@ -16870,7 +16870,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：定义 Device Profile v0 契约；检查“Schema 覆盖本 PRD 的 12 类交互”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E30" s="91" t="n">
         <x:v>8</x:v>
@@ -16897,7 +16897,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
+    <x:row r="31" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A31" s="91" t="n">
         <x:v>30</x:v>
       </x:c>
@@ -16917,7 +16917,7 @@
 Dependencies
 - ZW-ST-0201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：注册设备能力并供 UI 查询；检查“API 返回 capability_id、动作、参数、权限、风险和状态 Schema”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E31" s="91" t="n">
         <x:v>8</x:v>
@@ -16944,7 +16944,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A32" s="91" t="n">
         <x:v>31</x:v>
       </x:c>
@@ -16964,7 +16964,7 @@
 Dependencies
 - ZW-ST-0201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：建立家庭 Ontology v0；检查“Ontology 有版本和迁移记录”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E32" s="91" t="n">
         <x:v>8</x:v>
@@ -16991,7 +16991,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
+    <x:row r="33" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A33" s="91" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -17011,7 +17011,7 @@
 Dependencies
 - ZW-ST-0201,ZW-ST-0203
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：能力 Schema 兼容迁移；检查“升级前给出兼容性检查”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E33" s="91" t="n">
         <x:v>8</x:v>
@@ -17038,7 +17038,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
+    <x:row r="34" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A34" s="91" t="n">
         <x:v>33</x:v>
       </x:c>
@@ -17052,13 +17052,13 @@
         <x:v>Logical ID: ZW-ST-0301
 作为家庭成员，我打开首页时能看到设备状态和状态时间。
 Acceptance Criteria
-- 局域网目标 2 秒内返回快照；每个状态含 observed_at 和 freshness；不可用值显示未知而非 0。
+- 局域网目标 2 秒内返回快照；每个状态含 observed_at 和 freshness；不可用值显示未知而非 0；在目标环境采样中，95% 在线设备状态在定义的心跳窗口内更新。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：读取家庭状态快照；检查“局域网目标 2 秒内返回快照”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E34" s="91" t="n">
         <x:v>9</x:v>
@@ -17085,7 +17085,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
+    <x:row r="35" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A35" s="91" t="n">
         <x:v>34</x:v>
       </x:c>
@@ -17105,7 +17105,7 @@
 Dependencies
 - ZW-ST-0301,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：订阅设备与任务事件；检查“SSE 或等价事件流支持断线重连和游标续传”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E35" s="91" t="n">
         <x:v>9</x:v>
@@ -17132,7 +17132,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
+    <x:row r="36" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A36" s="91" t="n">
         <x:v>35</x:v>
       </x:c>
@@ -17152,7 +17152,7 @@
 Dependencies
 - ZW-ST-0301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：离线设备浅灰遮罩；检查“离线判定使用心跳窗口”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E36" s="91" t="n">
         <x:v>9</x:v>
@@ -17179,7 +17179,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
+    <x:row r="37" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A37" s="91" t="n">
         <x:v>36</x:v>
       </x:c>
@@ -17193,13 +17193,13 @@
         <x:v>Logical ID: ZW-ST-0304
 作为家庭成员，我能分辨系统正在尝试的状态和设备已确认的状态。
 Acceptance Criteria
-- 任务运行时展示 pending/running；只在设备上报或回查成功后更新 confirmed state；超时显示不确定。
+- 任务运行时展示 pending/running；只在设备上报或回查成功后更新 confirmed state；超时显示不确定；任务“成功”与设备真实状态一致率 ≥ 99%。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-0302
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：区分期望状态与确认状态；检查“任务运行时展示 pending/running”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E37" s="91" t="n">
         <x:v>9</x:v>
@@ -17226,7 +17226,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
+    <x:row r="38" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A38" s="91" t="n">
         <x:v>37</x:v>
       </x:c>
@@ -17246,7 +17246,7 @@
 Dependencies
 - ZW-ST-0101,ZW-ST-0301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：展示家庭网络拓扑；检查“拓扑支持父子链路、连接类型和节点状态”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E38" s="91" t="n">
         <x:v>10</x:v>
@@ -17273,7 +17273,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
+    <x:row r="39" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A39" s="91" t="n">
         <x:v>38</x:v>
       </x:c>
@@ -17293,7 +17293,7 @@
 Dependencies
 - ZW-ST-0401
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：查看网络节点健康度；检查“节点详情字段来源明确”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E39" s="91" t="n">
         <x:v>10</x:v>
@@ -17320,7 +17320,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
+    <x:row r="40" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A40" s="91" t="n">
         <x:v>39</x:v>
       </x:c>
@@ -17340,7 +17340,7 @@
 Dependencies
 - ZW-ST-0401
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：从拓扑进入设备详情；检查“有关联 device_id 的节点可打开设备详情”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E40" s="91" t="n">
         <x:v>10</x:v>
@@ -17367,7 +17367,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
+    <x:row r="41" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A41" s="91" t="n">
         <x:v>40</x:v>
       </x:c>
@@ -17381,13 +17381,13 @@
         <x:v>Logical ID: ZW-ST-0501
 作为家庭成员，我能按房间扫描所有关键设备和状态。
 Acceptance Criteria
-- 卡片按建筑/楼层/房间稳定排序；房间标题显示聚合状态；未归属设备进入待整理分组。
+- 卡片按建筑/楼层/房间稳定排序；房间标题显示聚合状态；未归属设备进入待整理分组；80% 的常用动作可在首页两次交互内完成。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-0101,ZW-ST-0301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：按房间归类首页卡片；检查“卡片按建筑/楼层/房间稳定排序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E41" s="91" t="n">
         <x:v>11</x:v>
@@ -17414,7 +17414,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
+    <x:row r="42" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A42" s="91" t="n">
         <x:v>41</x:v>
       </x:c>
@@ -17434,7 +17434,7 @@
 Dependencies
 - ZW-ST-0501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：有限尺寸 Widget 网格；检查“仅允许预定义尺寸”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E42" s="91" t="n">
         <x:v>11</x:v>
@@ -17461,7 +17461,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
+    <x:row r="43" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A43" s="91" t="n">
         <x:v>42</x:v>
       </x:c>
@@ -17481,7 +17481,7 @@
 Dependencies
 - ZW-ST-0501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：卡片与户型图二级视图；检查“默认进入卡片视图”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E43" s="91" t="n">
         <x:v>11</x:v>
@@ -17508,7 +17508,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
+    <x:row r="44" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A44" s="91" t="n">
         <x:v>43</x:v>
       </x:c>
@@ -17528,7 +17528,7 @@
 Dependencies
 - ZW-ST-0202,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：空调温度步进控件；检查“控件显示允许范围”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E44" s="91" t="n">
         <x:v>12</x:v>
@@ -17555,7 +17555,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="45">
+    <x:row r="45" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A45" s="91" t="n">
         <x:v>44</x:v>
       </x:c>
@@ -17575,7 +17575,7 @@
 Dependencies
 - ZW-ST-0202,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：可调灯开关与亮度滑条；检查“开关关闭时滑条隐藏”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E45" s="91" t="n">
         <x:v>12</x:v>
@@ -17602,7 +17602,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
+    <x:row r="46" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A46" s="91" t="n">
         <x:v>45</x:v>
       </x:c>
@@ -17622,7 +17622,7 @@
 Dependencies
 - ZW-ST-1202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：对开窗帘开停关交互；检查“打开完成显示 0%，关闭完成显示 100%”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E46" s="91" t="n">
         <x:v>12</x:v>
@@ -17649,7 +17649,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="47">
+    <x:row r="47" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A47" s="91" t="n">
         <x:v>46</x:v>
       </x:c>
@@ -17669,7 +17669,7 @@
 Dependencies
 - ZW-ST-1202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：卷帘开停关交互；检查“开为 0%、关为 100%”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E47" s="91" t="n">
         <x:v>12</x:v>
@@ -17696,7 +17696,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="48">
+    <x:row r="48" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A48" s="91" t="n">
         <x:v>47</x:v>
       </x:c>
@@ -17716,7 +17716,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：鱼缸灯光与投食交互；检查“投食期间按钮显示旋转状态且不可重复提交”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E48" s="91" t="n">
         <x:v>12</x:v>
@@ -17743,7 +17743,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
+    <x:row r="49" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A49" s="91" t="n">
         <x:v>48</x:v>
       </x:c>
@@ -17763,7 +17763,7 @@
 Dependencies
 - ZW-ST-1503
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：智能插座与用电统计；检查“统计口径和更新时间可见”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E49" s="91" t="n">
         <x:v>12</x:v>
@@ -17790,7 +17790,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="50">
+    <x:row r="50" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A50" s="91" t="n">
         <x:v>49</x:v>
       </x:c>
@@ -17810,7 +17810,7 @@
 Dependencies
 - ZW-ST-1503,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：路由器安全重启；检查“点击后显示影响范围与预计离线时间”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E50" s="91" t="n">
         <x:v>12</x:v>
@@ -17837,7 +17837,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="51">
+    <x:row r="51" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A51" s="91" t="n">
         <x:v>50</x:v>
       </x:c>
@@ -17857,7 +17857,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：扫地机器人全屋清洁快捷操作；检查“首页仅有全屋清洁”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E51" s="91" t="n">
         <x:v>12</x:v>
@@ -17884,7 +17884,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="52">
+    <x:row r="52" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A52" s="91" t="n">
         <x:v>51</x:v>
       </x:c>
@@ -17904,7 +17904,7 @@
 Dependencies
 - ZW-ST-1502
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：长按语音设备指令；检查“界面明确提示按住说话”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E52" s="91" t="n">
         <x:v>12</x:v>
@@ -17931,7 +17931,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
+    <x:row r="53" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A53" s="91" t="n">
         <x:v>52</x:v>
       </x:c>
@@ -17951,7 +17951,7 @@
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：个人电子设备只读状态；检查“卡片仅展示在线、网络和最后心跳”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E53" s="91" t="n">
         <x:v>12</x:v>
@@ -17978,7 +17978,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="54">
+    <x:row r="54" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A54" s="91" t="n">
         <x:v>53</x:v>
       </x:c>
@@ -17998,7 +17998,7 @@
 Dependencies
 - ZW-ST-1602
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：中枢额度与数据中心指标卡；检查“额度显示 5 小时、周限额和预充值余额及更新时间”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E54" s="91" t="n">
         <x:v>12</x:v>
@@ -18025,7 +18025,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="55">
+    <x:row r="55" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A55" s="91" t="n">
         <x:v>54</x:v>
       </x:c>
@@ -18045,7 +18045,7 @@
 Dependencies
 - ZW-ST-0501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：四档响应式网格；检查“折叠外屏压缩为单列重点信息”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E55" s="91" t="n">
         <x:v>13</x:v>
@@ -18072,7 +18072,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="56">
+    <x:row r="56" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A56" s="91" t="n">
         <x:v>55</x:v>
       </x:c>
@@ -18092,7 +18092,7 @@
 Dependencies
 - ZW-ST-0701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：无限信息流与侧边栏版权；检查“主内容自然滚动”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E56" s="91" t="n">
         <x:v>13</x:v>
@@ -18119,7 +18119,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="57">
+    <x:row r="57" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A57" s="91" t="n">
         <x:v>56</x:v>
       </x:c>
@@ -18139,7 +18139,7 @@
 Dependencies
 - ZW-ST-0701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：键盘、读屏与减少动态效果；检查“控件有可访问名称和焦点顺序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E57" s="91" t="n">
         <x:v>13</x:v>
@@ -18166,7 +18166,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="58">
+    <x:row r="58" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A58" s="91" t="n">
         <x:v>57</x:v>
       </x:c>
@@ -18186,7 +18186,7 @@
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：添加单设备动作卡；检查“只能选择设备已注册的动作”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E58" s="91" t="n">
         <x:v>14</x:v>
@@ -18213,7 +18213,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="59">
+    <x:row r="59" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A59" s="91" t="n">
         <x:v>58</x:v>
       </x:c>
@@ -18233,7 +18233,7 @@
 Dependencies
 - ZW-ST-0801
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：在一张卡中组合并行动作；检查“同卡动作无依赖时并行执行”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E59" s="91" t="n">
         <x:v>14</x:v>
@@ -18260,7 +18260,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="60">
+    <x:row r="60" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A60" s="91" t="n">
         <x:v>59</x:v>
       </x:c>
@@ -18280,7 +18280,7 @@
 Dependencies
 - ZW-ST-0802
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：步骤排序与依赖校验；检查“支持拖动和键盘排序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E60" s="91" t="n">
         <x:v>14</x:v>
@@ -18307,7 +18307,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="61">
+    <x:row r="61" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A61" s="91" t="n">
         <x:v>60</x:v>
       </x:c>
@@ -18327,7 +18327,7 @@
 Dependencies
 - ZW-ST-0803
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：场景草稿、Review 与发布；检查“草稿和已发布版本分离”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E61" s="91" t="n">
         <x:v>14</x:v>
@@ -18354,7 +18354,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="62">
+    <x:row r="62" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A62" s="91" t="n">
         <x:v>61</x:v>
       </x:c>
@@ -18374,7 +18374,7 @@
 Dependencies
 - ZW-ST-0804,ZW-ST-1101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 场景走查/指标验收：观影模式预置场景；检查“包含窗帘、灯、电视、Apple TV/Infuse、NAS 推荐和语音播报”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E62" s="91" t="n">
         <x:v>15</x:v>
@@ -18401,7 +18401,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="63">
+    <x:row r="63" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A63" s="91" t="n">
         <x:v>62</x:v>
       </x:c>
@@ -18421,7 +18421,7 @@
 Dependencies
 - ZW-ST-0804,ZW-ST-1101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 场景走查/指标验收：离家模式预置场景；检查“按能力发现目标而非写死设备清单”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E63" s="91" t="n">
         <x:v>15</x:v>
@@ -18448,7 +18448,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="64">
+    <x:row r="64" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A64" s="91" t="n">
         <x:v>63</x:v>
       </x:c>
@@ -18468,7 +18468,7 @@
 Dependencies
 - ZW-ST-1401,ZW-ST-0801
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：自然语言生成场景草稿；检查“系统展示解析出的意图、设备、动作和假设”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E64" s="91" t="n">
         <x:v>16</x:v>
@@ -18495,7 +18495,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="65">
+    <x:row r="65" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A65" s="91" t="n">
         <x:v>64</x:v>
       </x:c>
@@ -18515,7 +18515,7 @@
 Dependencies
 - ZW-ST-1402
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：Skill 匹配与 Plan Mode 分流；检查“路由结果含匹配依据和置信度”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E65" s="91" t="n">
         <x:v>16</x:v>
@@ -18542,7 +18542,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="66">
+    <x:row r="66" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A66" s="91" t="n">
         <x:v>65</x:v>
       </x:c>
@@ -18562,7 +18562,7 @@
 Dependencies
 - ZW-ST-1303,ZW-ST-1103
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：下载电影长程工作流；检查“计划调用 NAS 搜索 MCP、过滤候选、下载 MCP、等待完成和微信通知”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E66" s="91" t="n">
         <x:v>16</x:v>
@@ -18589,7 +18589,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="67">
+    <x:row r="67" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A67" s="91" t="n">
         <x:v>66</x:v>
       </x:c>
@@ -18603,13 +18603,13 @@
         <x:v>Logical ID: ZW-ST-1101
 作为家庭成员，我触发场景后能看到每张卡和卡内动作的实时状态。
 Acceptance Criteria
-- 状态包含等待、运行、成功、失败、跳过和待确认；页面刷新后能恢复同一运行实例。
+- 状态包含等待、运行、成功、失败、跳过和待确认；页面刷新后能恢复同一运行实例；已发布场景完整执行成功率 ≥ 95%，失败步骤可定位。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-1201,ZW-ST-0302
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：逐卡执行并展示结果；检查“状态包含等待、运行、成功、失败、跳过和待确认”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E67" s="91" t="n">
         <x:v>17</x:v>
@@ -18636,7 +18636,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="68">
+    <x:row r="68" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A68" s="91" t="n">
         <x:v>67</x:v>
       </x:c>
@@ -18656,7 +18656,7 @@
 Dependencies
 - ZW-ST-1101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：失败策略、重试与取消；检查“错误码映射为可行动说明”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E68" s="91" t="n">
         <x:v>17</x:v>
@@ -18683,7 +18683,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="69">
+    <x:row r="69" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A69" s="91" t="n">
         <x:v>68</x:v>
       </x:c>
@@ -18703,7 +18703,7 @@
 Dependencies
 - ZW-ST-1203
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：长程流程断点续跑；检查“关键节点写入 checkpointer”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E69" s="91" t="n">
         <x:v>17</x:v>
@@ -18730,7 +18730,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="70">
+    <x:row r="70" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A70" s="91" t="n">
         <x:v>69</x:v>
       </x:c>
@@ -18750,7 +18750,7 @@
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：统一异步任务契约；检查“任务含 idempotency_key、发起者、目标、参数、风险、超时、重试、trace_id 和标准状态机”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E70" s="91" t="n">
         <x:v>18</x:v>
@@ -18777,7 +18777,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
+    <x:row r="71" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A71" s="91" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -18797,7 +18797,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：优先队列强制状态上报；检查“优先队列拒绝同步任务”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E71" s="91" t="n">
         <x:v>18</x:v>
@@ -18824,7 +18824,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="72">
+    <x:row r="72" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A72" s="91" t="n">
         <x:v>71</x:v>
       </x:c>
@@ -18844,7 +18844,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：超时、重试和死信恢复；检查“重试次数与退避可配置”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E72" s="91" t="n">
         <x:v>18</x:v>
@@ -18871,7 +18871,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="73">
+    <x:row r="73" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A73" s="91" t="n">
         <x:v>72</x:v>
       </x:c>
@@ -18891,7 +18891,7 @@
 Dependencies
 - ZW-ST-1202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：任务队列双视图；检查“两类队列可筛选”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E73" s="91" t="n">
         <x:v>18</x:v>
@@ -18918,7 +18918,7 @@
         <x:v>In Progress</x:v>
       </x:c>
     </x:row>
-    <x:row r="74">
+    <x:row r="74" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A74" s="91" t="n">
         <x:v>73</x:v>
       </x:c>
@@ -18938,7 +18938,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：MCP 工具发现与能力白名单；检查“网关按身份、角色、设备和风险返回白名单”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E74" s="91" t="n">
         <x:v>19</x:v>
@@ -18965,7 +18965,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="75">
+    <x:row r="75" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A75" s="91" t="n">
         <x:v>74</x:v>
       </x:c>
@@ -18985,7 +18985,7 @@
 Dependencies
 - ZW-ST-0201,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：设备适配器标准接口；检查“接口有契约测试”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E75" s="91" t="n">
         <x:v>19</x:v>
@@ -19012,7 +19012,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="76">
+    <x:row r="76" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A76" s="91" t="n">
         <x:v>75</x:v>
       </x:c>
@@ -19032,7 +19032,7 @@
 Dependencies
 - ZW-ST-1302
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：首批真实服务与设备接入；检查“至少 5 类真实接入通过读写/只读能力声明”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E76" s="91" t="n">
         <x:v>19</x:v>
@@ -19059,7 +19059,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="77">
+    <x:row r="77" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A77" s="91" t="n">
         <x:v>76</x:v>
       </x:c>
@@ -19079,7 +19079,7 @@
 Dependencies
 - ZW-ST-1503
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：意图与风险分级；检查“分类结果可解释且进入审计”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E77" s="91" t="n">
         <x:v>20</x:v>
@@ -19106,7 +19106,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="78">
+    <x:row r="78" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A78" s="91" t="n">
         <x:v>77</x:v>
       </x:c>
@@ -19126,7 +19126,7 @@
 Dependencies
 - ZW-ST-1401,ZW-ST-1301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：Planner 生成受约束任务图；检查“计划无循环”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E78" s="91" t="n">
         <x:v>20</x:v>
@@ -19153,7 +19153,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="79">
+    <x:row r="79" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A79" s="91" t="n">
         <x:v>78</x:v>
       </x:c>
@@ -19173,7 +19173,7 @@
 Dependencies
 - ZW-ST-1402
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：计划人工审阅与修改；检查“修改后重新校验权限与依赖”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E79" s="91" t="n">
         <x:v>20</x:v>
@@ -19200,7 +19200,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="80">
+    <x:row r="80" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A80" s="91" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -19220,7 +19220,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：端到端身份透传与工具侧鉴权；检查“OIDC→会话→JWT→Agent→MCP→数据层身份不断链”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E80" s="91" t="n">
         <x:v>21</x:v>
@@ -19247,7 +19247,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="81">
+    <x:row r="81" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A81" s="91" t="n">
         <x:v>80</x:v>
       </x:c>
@@ -19267,7 +19267,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：角色与儿童策略；检查“kid 请求强制经过 Compliance”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E81" s="91" t="n">
         <x:v>21</x:v>
@@ -19294,7 +19294,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="82">
+    <x:row r="82" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A82" s="91" t="n">
         <x:v>81</x:v>
       </x:c>
@@ -19308,13 +19308,13 @@
         <x:v>Logical ID: ZW-ST-1503
 作为家庭成员，我在重启路由器或断开关键插座前能看到影响并明确确认。
 Acceptance Criteria
-- 准备阶段返回影响范围和确认令牌；令牌短期有效且绑定参数；执行与确认人都被审计。
+- 准备阶段返回影响范围和确认令牌；令牌短期有效且绑定参数；执行与确认人都被审计；100% 高风险动作在执行前完成明确确认，确认令牌绑定动作参数。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：高风险动作 prepare/confirm/execute；检查“准备阶段返回影响范围和确认令牌”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E82" s="91" t="n">
         <x:v>21</x:v>
@@ -19341,7 +19341,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="83">
+    <x:row r="83" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A83" s="91" t="n">
         <x:v>82</x:v>
       </x:c>
@@ -19361,7 +19361,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：不可变审计查询；检查“审计事件追加写”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E83" s="91" t="n">
         <x:v>21</x:v>
@@ -19388,7 +19388,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="84">
+    <x:row r="84" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A84" s="91" t="n">
         <x:v>83</x:v>
       </x:c>
@@ -19408,7 +19408,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：全链路 trace 关联；检查“各层共享 trace_id”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E84" s="91" t="n">
         <x:v>22</x:v>
@@ -19435,7 +19435,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="85">
+    <x:row r="85" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A85" s="91" t="n">
         <x:v>84</x:v>
       </x:c>
@@ -19455,7 +19455,7 @@
 Dependencies
 - ZW-ST-1601
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：模型用量与预算面板；检查“每个指标显示来源、时间和不可用状态”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E85" s="91" t="n">
         <x:v>22</x:v>
@@ -19482,7 +19482,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="86">
+    <x:row r="86" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A86" s="91" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -19502,7 +19502,7 @@
 Dependencies
 - ZW-ST-1601
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：家庭基础设施健康面板；检查“指标带时间窗”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E86" s="91" t="n">
         <x:v>22</x:v>
@@ -19529,7 +19529,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="87">
+    <x:row r="87" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A87" s="91" t="n">
         <x:v>86</x:v>
       </x:c>
@@ -19549,7 +19549,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：稳定需求 ID 与父子关系；检查“Roadmap、Epic、Story、Task ID 唯一”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E87" s="91" t="n">
         <x:v>23</x:v>
@@ -19576,7 +19576,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="88">
+    <x:row r="88" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A88" s="91" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -19596,7 +19596,7 @@
 Dependencies
 - ZW-ST-1701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：Story 结构化契约；检查“必填字段有数据字典与枚举”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E88" s="91" t="n">
         <x:v>23</x:v>
@@ -19623,7 +19623,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="89">
+    <x:row r="89" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A89" s="91" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -19637,13 +19637,13 @@
         <x:v>Logical ID: ZW-ST-1703
 作为维护者，我能从 Story 找到架构决策、测试、缺陷、代码和发布。
 Acceptance Criteria
-- PR 必须引用 Story；架构变化必须引用 ADR；Done 前测试证据齐全且阻塞缺陷关闭。
+- PR 必须引用 Story；架构变化必须引用 ADR；Done 前测试证据齐全且阻塞缺陷关闭；100% 发布变更可回溯到 Story、测试证据、PR、版本和运行 trace。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-1702
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：ADR/TC/BUG/PR/Release 追溯门禁；检查“PR 必须引用 Story”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E89" s="91" t="n">
         <x:v>23</x:v>
@@ -19670,7 +19670,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="90">
+    <x:row r="90" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A90" s="91" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -19690,7 +19690,7 @@
 Dependencies
 - ZW-ST-1701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：Jira 与 GitHub 可移植导入视图；检查“Jira Standard、Jira Advanced 和 GitHub 视图保留逻辑 ID”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E90" s="91" t="n">
         <x:v>23</x:v>
@@ -19717,7 +19717,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="91">
+    <x:row r="91" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A91" s="91" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -19737,7 +19737,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：NAS 容器化部署；检查“部署不依赖开发机”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E91" s="91" t="n">
         <x:v>24</x:v>
@@ -19764,7 +19764,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="92">
+    <x:row r="92" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A92" s="91" t="n">
         <x:v>91</x:v>
       </x:c>
@@ -19784,7 +19784,7 @@
 Dependencies
 - ZW-ST-1801
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：安全升级与回滚；检查“发布前备份”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E92" s="91" t="n">
         <x:v>24</x:v>
@@ -19811,7 +19811,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="93">
+    <x:row r="93" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A93" s="91" t="n">
         <x:v>92</x:v>
       </x:c>
@@ -19831,7 +19831,7 @@
 Dependencies
 - ZW-ST-1801,ZW-ST-1203
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：局域网降级与灾难恢复；检查“核心控制不依赖公网”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="E93" s="91" t="n">
         <x:v>24</x:v>
@@ -19858,7 +19858,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="94">
+    <x:row r="94" ht="198" hidden="0" customHeight="1">
       <x:c r="A94" s="91" t="n">
         <x:v>93</x:v>
       </x:c>
@@ -19903,7 +19903,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="95">
+    <x:row r="95" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A95" s="91" t="n">
         <x:v>94</x:v>
       </x:c>
@@ -19948,7 +19948,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="96">
+    <x:row r="96" ht="198" hidden="0" customHeight="1">
       <x:c r="A96" s="91" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -19993,7 +19993,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="97">
+    <x:row r="97" ht="198" hidden="0" customHeight="1">
       <x:c r="A97" s="91" t="n">
         <x:v>96</x:v>
       </x:c>
@@ -20038,7 +20038,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="98">
+    <x:row r="98" ht="198" hidden="0" customHeight="1">
       <x:c r="A98" s="91" t="n">
         <x:v>97</x:v>
       </x:c>
@@ -20083,7 +20083,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="99">
+    <x:row r="99" ht="198" hidden="0" customHeight="1">
       <x:c r="A99" s="91" t="n">
         <x:v>98</x:v>
       </x:c>
@@ -20128,7 +20128,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="100">
+    <x:row r="100" ht="198" hidden="0" customHeight="1">
       <x:c r="A100" s="91" t="n">
         <x:v>99</x:v>
       </x:c>
@@ -20173,7 +20173,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="101">
+    <x:row r="101" ht="198" hidden="0" customHeight="1">
       <x:c r="A101" s="91" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -20218,7 +20218,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="102">
+    <x:row r="102" ht="198" hidden="0" customHeight="1">
       <x:c r="A102" s="91" t="n">
         <x:v>101</x:v>
       </x:c>
@@ -20263,7 +20263,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="103">
+    <x:row r="103" ht="198" hidden="0" customHeight="1">
       <x:c r="A103" s="91" t="n">
         <x:v>102</x:v>
       </x:c>
@@ -20308,7 +20308,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="104">
+    <x:row r="104" ht="198" hidden="0" customHeight="1">
       <x:c r="A104" s="91" t="n">
         <x:v>103</x:v>
       </x:c>
@@ -20353,7 +20353,7 @@
         <x:v>Draft</x:v>
       </x:c>
     </x:row>
-    <x:row r="105">
+    <x:row r="105" ht="198" hidden="0" customHeight="1">
       <x:c r="A105" s="91" t="n">
         <x:v>104</x:v>
       </x:c>
@@ -20401,7 +20401,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89f1223faf3e4f45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4f803110b6e4d97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20465,11 +20465,11 @@
         <x:v>Evidence Link</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="198" hidden="0" customHeight="1">
       <x:c r="A2" s="91" t="str">
         <x:v>[ZW-RM-01] 可信设备孪生</x:v>
       </x:c>
-      <x:c r="B2" s="91" t="str">
+      <x:c r="B2" s="92" t="str">
         <x:v>Logical ID: ZW-RM-01
 让家庭中的空间、网络、设备、能力和状态形成可信、可扩展的数字映射。
 Acceptance Criteria
@@ -20504,11 +20504,11 @@
       <x:c r="K2" s="91"/>
       <x:c r="L2" s="91"/>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="198" hidden="0" customHeight="1">
       <x:c r="A3" s="91" t="str">
         <x:v>[ZW-RM-02] 自然设备交互</x:v>
       </x:c>
-      <x:c r="B3" s="91" t="str">
+      <x:c r="B3" s="92" t="str">
         <x:v>Logical ID: ZW-RM-02
 让不同设备的控制方式一眼可懂，并在手机、折叠屏、平板和桌面保持一致。
 Acceptance Criteria
@@ -20543,11 +20543,11 @@
       <x:c r="K3" s="91"/>
       <x:c r="L3" s="91"/>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="198" hidden="0" customHeight="1">
       <x:c r="A4" s="91" t="str">
         <x:v>[ZW-RM-03] 场景与流程</x:v>
       </x:c>
-      <x:c r="B4" s="91" t="str">
+      <x:c r="B4" s="92" t="str">
         <x:v>Logical ID: ZW-RM-03
 把多设备动作组织成可审阅、可发布、可逐步执行的家庭场景和长程流程。
 Acceptance Criteria
@@ -20582,11 +20582,11 @@
       <x:c r="K4" s="91"/>
       <x:c r="L4" s="91"/>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="198" hidden="0" customHeight="1">
       <x:c r="A5" s="91" t="str">
         <x:v>[ZW-RM-04] Agent 与 MCP 平台</x:v>
       </x:c>
-      <x:c r="B5" s="91" t="str">
+      <x:c r="B5" s="92" t="str">
         <x:v>Logical ID: ZW-RM-04
 用统一任务契约、MCP 网关和 Agent 编排安全地连接设备与家庭服务。
 Acceptance Criteria
@@ -20621,11 +20621,11 @@
       <x:c r="K5" s="91"/>
       <x:c r="L5" s="91"/>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="198" hidden="0" customHeight="1">
       <x:c r="A6" s="91" t="str">
         <x:v>[ZW-RM-05] 安全与治理</x:v>
       </x:c>
-      <x:c r="B6" s="91" t="str">
+      <x:c r="B6" s="92" t="str">
         <x:v>Logical ID: ZW-RM-05
 让权限、风险、审计、成本和运行状态可控、可查、可回溯。
 Acceptance Criteria
@@ -20660,11 +20660,11 @@
       <x:c r="K6" s="91"/>
       <x:c r="L6" s="91"/>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="198" hidden="0" customHeight="1">
       <x:c r="A7" s="91" t="str">
         <x:v>[ZW-RM-06] 工程交付与运营</x:v>
       </x:c>
-      <x:c r="B7" s="91" t="str">
+      <x:c r="B7" s="92" t="str">
         <x:v>Logical ID: ZW-RM-06
 把产品定义、架构、需求、代码、测试、发布和运行证据连成一条可自动读取的链。
 Acceptance Criteria
@@ -20699,11 +20699,11 @@
       <x:c r="K7" s="91"/>
       <x:c r="L7" s="91"/>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="198" hidden="0" customHeight="1">
       <x:c r="A8" s="91" t="str">
         <x:v>[ZW-EP-01] 空间与设备登记</x:v>
       </x:c>
-      <x:c r="B8" s="91" t="str">
+      <x:c r="B8" s="92" t="str">
         <x:v>Logical ID: ZW-EP-01
 建立 Home→Building→Floor→Room→Device 的可扩展空间模型和设备登记流程。
 Acceptance Criteria
@@ -20740,11 +20740,11 @@
       <x:c r="K8" s="91"/>
       <x:c r="L8" s="91"/>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="198" hidden="0" customHeight="1">
       <x:c r="A9" s="91" t="str">
         <x:v>[ZW-EP-02] Device Profile 与 Ontology</x:v>
       </x:c>
-      <x:c r="B9" s="91" t="str">
+      <x:c r="B9" s="92" t="str">
         <x:v>Logical ID: ZW-EP-02
 用受版本管理的能力模型屏蔽品牌差异，并供 UI、Agent、MCP 共用。
 Acceptance Criteria
@@ -20781,11 +20781,11 @@
       <x:c r="K9" s="91"/>
       <x:c r="L9" s="91"/>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="198" hidden="0" customHeight="1">
       <x:c r="A10" s="91" t="str">
         <x:v>[ZW-EP-03] 状态同步与离线语义</x:v>
       </x:c>
-      <x:c r="B10" s="91" t="str">
+      <x:c r="B10" s="92" t="str">
         <x:v>Logical ID: ZW-EP-03
 区分期望状态、确认状态和状态新鲜度，避免把请求成功当成设备完成。
 Acceptance Criteria
@@ -20822,11 +20822,11 @@
       <x:c r="K10" s="91"/>
       <x:c r="L10" s="91"/>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="198" hidden="0" customHeight="1">
       <x:c r="A11" s="91" t="str">
         <x:v>[ZW-EP-04] 网络拓扑</x:v>
       </x:c>
-      <x:c r="B11" s="91" t="str">
+      <x:c r="B11" s="92" t="str">
         <x:v>Logical ID: ZW-EP-04
 看清家庭网络节点、连接关系、健康状态和设备归属。
 Acceptance Criteria
@@ -20863,11 +20863,11 @@
       <x:c r="K11" s="91"/>
       <x:c r="L11" s="91"/>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="198" hidden="0" customHeight="1">
       <x:c r="A12" s="91" t="str">
         <x:v>[ZW-EP-05] 按房间的 Widget 首页</x:v>
       </x:c>
-      <x:c r="B12" s="91" t="str">
+      <x:c r="B12" s="92" t="str">
         <x:v>Logical ID: ZW-EP-05
 用有限尺寸卡片承载高密度信息和高频动作。
 Acceptance Criteria
@@ -20904,11 +20904,11 @@
       <x:c r="K12" s="91"/>
       <x:c r="L12" s="91"/>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="198" hidden="0" customHeight="1">
       <x:c r="A13" s="91" t="str">
         <x:v>[ZW-EP-06] 标准化设备控件</x:v>
       </x:c>
-      <x:c r="B13" s="91" t="str">
+      <x:c r="B13" s="92" t="str">
         <x:v>Logical ID: ZW-EP-06
 按能力生成可预测的设备交互，并为异步状态提供明确反馈。
 Acceptance Criteria
@@ -20945,11 +20945,11 @@
       <x:c r="K13" s="91"/>
       <x:c r="L13" s="91"/>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="198" hidden="0" customHeight="1">
       <x:c r="A14" s="91" t="str">
         <x:v>[ZW-EP-07] 跨终端体验与可访问性</x:v>
       </x:c>
-      <x:c r="B14" s="91" t="str">
+      <x:c r="B14" s="92" t="str">
         <x:v>Logical ID: ZW-EP-07
 优先支持直板手机、折叠屏、13 英寸平板和 16 英寸桌面。
 Acceptance Criteria
@@ -20986,11 +20986,11 @@
       <x:c r="K14" s="91"/>
       <x:c r="L14" s="91"/>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="198" hidden="0" customHeight="1">
       <x:c r="A15" s="91" t="str">
         <x:v>[ZW-EP-08] 场景卡片编排器</x:v>
       </x:c>
-      <x:c r="B15" s="91" t="str">
+      <x:c r="B15" s="92" t="str">
         <x:v>Logical ID: ZW-EP-08
 通过 Device/Tool + Action 组合成可审阅的步骤卡。
 Acceptance Criteria
@@ -21027,11 +21027,11 @@
       <x:c r="K15" s="91"/>
       <x:c r="L15" s="91"/>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="198" hidden="0" customHeight="1">
       <x:c r="A16" s="91" t="str">
         <x:v>[ZW-EP-09] 预置家庭场景</x:v>
       </x:c>
-      <x:c r="B16" s="91" t="str">
+      <x:c r="B16" s="92" t="str">
         <x:v>Logical ID: ZW-EP-09
 交付观影、离家等可编辑、可复用的家庭场景。
 Acceptance Criteria
@@ -21068,11 +21068,11 @@
       <x:c r="K16" s="91"/>
       <x:c r="L16" s="91"/>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="198" hidden="0" customHeight="1">
       <x:c r="A17" s="91" t="str">
         <x:v>[ZW-EP-10] 自然语言工作流与 Plan Mode</x:v>
       </x:c>
-      <x:c r="B17" s="91" t="str">
+      <x:c r="B17" s="92" t="str">
         <x:v>Logical ID: ZW-EP-10
 从自然语言生成建议计划，在执行前完成人工审阅。
 Acceptance Criteria
@@ -21109,11 +21109,11 @@
       <x:c r="K17" s="91"/>
       <x:c r="L17" s="91"/>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="198" hidden="0" customHeight="1">
       <x:c r="A18" s="91" t="str">
         <x:v>[ZW-EP-11] 流程运行与结果</x:v>
       </x:c>
-      <x:c r="B18" s="91" t="str">
+      <x:c r="B18" s="92" t="str">
         <x:v>Logical ID: ZW-EP-11
 逐卡执行、反馈结果，并支持失败定位、重试、取消和恢复。
 Acceptance Criteria
@@ -21150,11 +21150,11 @@
       <x:c r="K18" s="91"/>
       <x:c r="L18" s="91"/>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="198" hidden="0" customHeight="1">
       <x:c r="A19" s="91" t="str">
         <x:v>[ZW-EP-12] 普通与优先任务队列</x:v>
       </x:c>
-      <x:c r="B19" s="91" t="str">
+      <x:c r="B19" s="92" t="str">
         <x:v>Logical ID: ZW-EP-12
 所有写操作任务化；过程敏感操作走只允许异步与状态上报的优先队列。
 Acceptance Criteria
@@ -21191,11 +21191,11 @@
       <x:c r="K19" s="91"/>
       <x:c r="L19" s="91"/>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="198" hidden="0" customHeight="1">
       <x:c r="A20" s="91" t="str">
         <x:v>[ZW-EP-13] MCP 网关与设备适配器</x:v>
       </x:c>
-      <x:c r="B20" s="91" t="str">
+      <x:c r="B20" s="92" t="str">
         <x:v>Logical ID: ZW-EP-13
 统一工具发现、鉴权、调用审计和厂商设备接入。
 Acceptance Criteria
@@ -21232,11 +21232,11 @@
       <x:c r="K20" s="91"/>
       <x:c r="L20" s="91"/>
     </x:row>
-    <x:row r="21">
+    <x:row r="21" ht="198" hidden="0" customHeight="1">
       <x:c r="A21" s="91" t="str">
         <x:v>[ZW-EP-14] IntentRouter 与 Planner</x:v>
       </x:c>
-      <x:c r="B21" s="91" t="str">
+      <x:c r="B21" s="92" t="str">
         <x:v>Logical ID: ZW-EP-14
 对意图、风险和复杂度分级，编排 Agent、Skill、Tool 与 MCP。
 Acceptance Criteria
@@ -21273,11 +21273,11 @@
       <x:c r="K21" s="91"/>
       <x:c r="L21" s="91"/>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="198" hidden="0" customHeight="1">
       <x:c r="A22" s="91" t="str">
         <x:v>[ZW-EP-15] 身份、策略与审计</x:v>
       </x:c>
-      <x:c r="B22" s="91" t="str">
+      <x:c r="B22" s="92" t="str">
         <x:v>Logical ID: ZW-EP-15
 以家庭成员为主体实施最小权限、工具侧鉴权、高风险确认和不可抵赖审计。
 Acceptance Criteria
@@ -21314,11 +21314,11 @@
       <x:c r="K22" s="91"/>
       <x:c r="L22" s="91"/>
     </x:row>
-    <x:row r="23">
+    <x:row r="23" ht="198" hidden="0" customHeight="1">
       <x:c r="A23" s="91" t="str">
         <x:v>[ZW-EP-16] 可观察性与成本治理</x:v>
       </x:c>
-      <x:c r="B23" s="91" t="str">
+      <x:c r="B23" s="92" t="str">
         <x:v>Logical ID: ZW-EP-16
 用统一 trace 串联请求、计划、工具、任务、设备事件、token 和成本。
 Acceptance Criteria
@@ -21355,11 +21355,11 @@
       <x:c r="K23" s="91"/>
       <x:c r="L23" s="91"/>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="198" hidden="0" customHeight="1">
       <x:c r="A24" s="91" t="str">
         <x:v>[ZW-EP-17] 需求到发布追溯</x:v>
       </x:c>
-      <x:c r="B24" s="91" t="str">
+      <x:c r="B24" s="92" t="str">
         <x:v>Logical ID: ZW-EP-17
 用稳定 ID、结构化文档和门禁把 Story、ADR、TC、BUG、PR、Release 串起来。
 Acceptance Criteria
@@ -21396,11 +21396,11 @@
       <x:c r="K24" s="91"/>
       <x:c r="L24" s="91"/>
     </x:row>
-    <x:row r="25">
+    <x:row r="25" ht="198" hidden="0" customHeight="1">
       <x:c r="A25" s="91" t="str">
         <x:v>[ZW-EP-18] NAS 部署与运行保障</x:v>
       </x:c>
-      <x:c r="B25" s="91" t="str">
+      <x:c r="B25" s="92" t="str">
         <x:v>Logical ID: ZW-EP-18
 在家庭 NAS/树莓派环境中安全部署、升级、回滚和恢复。
 Acceptance Criteria
@@ -21437,11 +21437,11 @@
       <x:c r="K25" s="91"/>
       <x:c r="L25" s="91"/>
     </x:row>
-    <x:row r="26">
+    <x:row r="26" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A26" s="91" t="str">
         <x:v>[ZW-ST-0101] 建立多建筑多楼层空间树</x:v>
       </x:c>
-      <x:c r="B26" s="91" t="str">
+      <x:c r="B26" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0101
 作为管理员，我能建立建筑、楼层和房间，以便当前平层和未来四层住宅使用同一模型。
 Acceptance Criteria
@@ -21451,7 +21451,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：建立多建筑多楼层空间树；检查“可创建、重命名、排序和停用空间节点”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C26" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21482,11 +21482,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
+    <x:row r="27" ht="264" hidden="0" customHeight="1">
       <x:c r="A27" s="91" t="str">
         <x:v>[ZW-ST-0102] 按 Device Profile 添加设备</x:v>
       </x:c>
-      <x:c r="B27" s="91" t="str">
+      <x:c r="B27" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0102
 作为管理员，我能选择设备模板并完成命名、连接参数和房间归属，以便设备进入家庭孪生。
 Acceptance Criteria
@@ -21496,7 +21496,7 @@
 Dependencies
 - ZW-ST-0201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：按 Device Profile 添加设备；检查“向导依次完成模板选择、命名、参数、空间归属和连接验证”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C27" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21529,11 +21529,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
+    <x:row r="28" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A28" s="91" t="str">
         <x:v>[ZW-ST-0103] 编辑设备参数与空间归属</x:v>
       </x:c>
-      <x:c r="B28" s="91" t="str">
+      <x:c r="B28" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0103
 作为管理员，我能修改设备显示名、连接参数和房间，而不改变稳定 device_id。
 Acceptance Criteria
@@ -21543,7 +21543,7 @@
 Dependencies
 - ZW-ST-0101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：编辑设备参数与空间归属；检查“保存后 device_id 不变”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C28" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21576,11 +21576,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
+    <x:row r="29" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A29" s="91" t="str">
         <x:v>[ZW-ST-0104] 设备详情渐进披露</x:v>
       </x:c>
-      <x:c r="B29" s="91" t="str">
+      <x:c r="B29" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0104
 作为家庭成员，我能从卡片进入详情页查看能力、诊断和低频设置。
 Acceptance Criteria
@@ -21590,7 +21590,7 @@
 Dependencies
 - ZW-ST-0102
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：设备详情渐进披露；检查“详情页展示状态、能力、任务历史和适配器信息”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C29" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21623,11 +21623,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
+    <x:row r="30" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A30" s="91" t="str">
         <x:v>[ZW-ST-0201] 定义 Device Profile v0 契约</x:v>
       </x:c>
-      <x:c r="B30" s="91" t="str">
+      <x:c r="B30" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0201
 作为集成开发者，我能用统一 Schema 描述设备状态、动作、参数、风险和控件建议。
 Acceptance Criteria
@@ -21637,7 +21637,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：定义 Device Profile v0 契约；检查“Schema 覆盖本 PRD 的 12 类交互”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C30" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21668,11 +21668,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
+    <x:row r="31" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A31" s="91" t="str">
         <x:v>[ZW-ST-0202] 注册设备能力并供 UI 查询</x:v>
       </x:c>
-      <x:c r="B31" s="91" t="str">
+      <x:c r="B31" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0202
 作为前端和 Agent，我能读取设备的可用能力，而不是按品牌猜测。
 Acceptance Criteria
@@ -21682,7 +21682,7 @@
 Dependencies
 - ZW-ST-0201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：注册设备能力并供 UI 查询；检查“API 返回 capability_id、动作、参数、权限、风险和状态 Schema”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C31" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21715,11 +21715,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A32" s="91" t="str">
         <x:v>[ZW-ST-0203] 建立家庭 Ontology v0</x:v>
       </x:c>
-      <x:c r="B32" s="91" t="str">
+      <x:c r="B32" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0203
 作为系统，我能表达空间、设备、网络节点、能力、成员、场景和任务之间的关系。
 Acceptance Criteria
@@ -21729,7 +21729,7 @@
 Dependencies
 - ZW-ST-0201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：建立家庭 Ontology v0；检查“Ontology 有版本和迁移记录”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C32" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21762,11 +21762,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
+    <x:row r="33" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A33" s="91" t="str">
         <x:v>[ZW-ST-0204] 能力 Schema 兼容迁移</x:v>
       </x:c>
-      <x:c r="B33" s="91" t="str">
+      <x:c r="B33" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0204
 作为管理员，我能升级 Device Profile 而不让已登记设备失效。
 Acceptance Criteria
@@ -21776,7 +21776,7 @@
 Dependencies
 - ZW-ST-0201,ZW-ST-0203
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：能力 Schema 兼容迁移；检查“升级前给出兼容性检查”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C33" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21809,21 +21809,21 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
+    <x:row r="34" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A34" s="91" t="str">
         <x:v>[ZW-ST-0301] 读取家庭状态快照</x:v>
       </x:c>
-      <x:c r="B34" s="91" t="str">
+      <x:c r="B34" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0301
 作为家庭成员，我打开首页时能看到设备状态和状态时间。
 Acceptance Criteria
-- 局域网目标 2 秒内返回快照；每个状态含 observed_at 和 freshness；不可用值显示未知而非 0。
+- 局域网目标 2 秒内返回快照；每个状态含 observed_at 和 freshness；不可用值显示未知而非 0；在目标环境采样中，95% 在线设备状态在定义的心跳窗口内更新。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：读取家庭状态快照；检查“局域网目标 2 秒内返回快照”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C34" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21856,11 +21856,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
+    <x:row r="35" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A35" s="91" t="str">
         <x:v>[ZW-ST-0302] 订阅设备与任务事件</x:v>
       </x:c>
-      <x:c r="B35" s="91" t="str">
+      <x:c r="B35" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0302
 作为家庭成员，我能看到设备状态和任务阶段的增量更新。
 Acceptance Criteria
@@ -21870,7 +21870,7 @@
 Dependencies
 - ZW-ST-0301,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：订阅设备与任务事件；检查“SSE 或等价事件流支持断线重连和游标续传”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C35" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21903,11 +21903,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
+    <x:row r="36" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A36" s="91" t="str">
         <x:v>[ZW-ST-0303] 离线设备浅灰遮罩</x:v>
       </x:c>
-      <x:c r="B36" s="91" t="str">
+      <x:c r="B36" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0303
 作为家庭成员，我能一眼识别离线设备且不会误触控制。
 Acceptance Criteria
@@ -21917,7 +21917,7 @@
 Dependencies
 - ZW-ST-0301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：离线设备浅灰遮罩；检查“离线判定使用心跳窗口”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C36" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21950,21 +21950,21 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
+    <x:row r="37" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A37" s="91" t="str">
         <x:v>[ZW-ST-0304] 区分期望状态与确认状态</x:v>
       </x:c>
-      <x:c r="B37" s="91" t="str">
+      <x:c r="B37" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0304
 作为家庭成员，我能分辨系统正在尝试的状态和设备已确认的状态。
 Acceptance Criteria
-- 任务运行时展示 pending/running；只在设备上报或回查成功后更新 confirmed state；超时显示不确定。
+- 任务运行时展示 pending/running；只在设备上报或回查成功后更新 confirmed state；超时显示不确定；任务“成功”与设备真实状态一致率 ≥ 99%。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-0302
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：区分期望状态与确认状态；检查“任务运行时展示 pending/running”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C37" s="91" t="str">
         <x:v>Feature</x:v>
@@ -21997,11 +21997,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
+    <x:row r="38" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A38" s="91" t="str">
         <x:v>[ZW-ST-0401] 展示家庭网络拓扑</x:v>
       </x:c>
-      <x:c r="B38" s="91" t="str">
+      <x:c r="B38" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0401
 作为管理员，我能查看互联网、路由器、中枢、NAS 和终端之间的连接关系。
 Acceptance Criteria
@@ -22011,7 +22011,7 @@
 Dependencies
 - ZW-ST-0101,ZW-ST-0301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：展示家庭网络拓扑；检查“拓扑支持父子链路、连接类型和节点状态”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C38" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22044,11 +22044,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
+    <x:row r="39" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A39" s="91" t="str">
         <x:v>[ZW-ST-0402] 查看网络节点健康度</x:v>
       </x:c>
-      <x:c r="B39" s="91" t="str">
+      <x:c r="B39" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0402
 作为管理员，我能查看 IP、上级节点、链路质量、最后心跳和告警。
 Acceptance Criteria
@@ -22058,7 +22058,7 @@
 Dependencies
 - ZW-ST-0401
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：查看网络节点健康度；检查“节点详情字段来源明确”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C39" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22091,11 +22091,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
+    <x:row r="40" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A40" s="91" t="str">
         <x:v>[ZW-ST-0403] 从拓扑进入设备详情</x:v>
       </x:c>
-      <x:c r="B40" s="91" t="str">
+      <x:c r="B40" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0403
 作为管理员，我能从网络节点跳到对应设备并查看控制影响。
 Acceptance Criteria
@@ -22105,7 +22105,7 @@
 Dependencies
 - ZW-ST-0401
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：从拓扑进入设备详情；检查“有关联 device_id 的节点可打开设备详情”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C40" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22138,21 +22138,21 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
+    <x:row r="41" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A41" s="91" t="str">
         <x:v>[ZW-ST-0501] 按房间归类首页卡片</x:v>
       </x:c>
-      <x:c r="B41" s="91" t="str">
+      <x:c r="B41" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0501
 作为家庭成员，我能按房间扫描所有关键设备和状态。
 Acceptance Criteria
-- 卡片按建筑/楼层/房间稳定排序；房间标题显示聚合状态；未归属设备进入待整理分组。
+- 卡片按建筑/楼层/房间稳定排序；房间标题显示聚合状态；未归属设备进入待整理分组；80% 的常用动作可在首页两次交互内完成。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-0101,ZW-ST-0301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：按房间归类首页卡片；检查“卡片按建筑/楼层/房间稳定排序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C41" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22185,11 +22185,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
+    <x:row r="42" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A42" s="91" t="str">
         <x:v>[ZW-ST-0502] 有限尺寸 Widget 网格</x:v>
       </x:c>
-      <x:c r="B42" s="91" t="str">
+      <x:c r="B42" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0502
 作为家庭成员，我能在不破坏阅读顺序的前提下调整卡片尺寸。
 Acceptance Criteria
@@ -22199,7 +22199,7 @@
 Dependencies
 - ZW-ST-0501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：有限尺寸 Widget 网格；检查“仅允许预定义尺寸”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C42" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22232,11 +22232,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
+    <x:row r="43" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A43" s="91" t="str">
         <x:v>[ZW-ST-0503] 卡片与户型图二级视图</x:v>
       </x:c>
-      <x:c r="B43" s="91" t="str">
+      <x:c r="B43" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0503
 作为家庭成员，我能在高密度卡片和空间化户型图之间切换。
 Acceptance Criteria
@@ -22246,7 +22246,7 @@
 Dependencies
 - ZW-ST-0501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：卡片与户型图二级视图；检查“默认进入卡片视图”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C43" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22279,11 +22279,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
+    <x:row r="44" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A44" s="91" t="str">
         <x:v>[ZW-ST-0601] 空调温度步进控件</x:v>
       </x:c>
-      <x:c r="B44" s="91" t="str">
+      <x:c r="B44" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0601
 作为家庭成员，我能用减号和加号按 1°C 调整目标温度。
 Acceptance Criteria
@@ -22293,7 +22293,7 @@
 Dependencies
 - ZW-ST-0202,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：空调温度步进控件；检查“控件显示允许范围”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C44" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22326,11 +22326,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="45">
+    <x:row r="45" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A45" s="91" t="str">
         <x:v>[ZW-ST-0602] 可调灯开关与亮度滑条</x:v>
       </x:c>
-      <x:c r="B45" s="91" t="str">
+      <x:c r="B45" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0602
 作为家庭成员，我打开灯后能展开亮度滑条，关闭后不显示滑条。
 Acceptance Criteria
@@ -22340,7 +22340,7 @@
 Dependencies
 - ZW-ST-0202,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：可调灯开关与亮度滑条；检查“开关关闭时滑条隐藏”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C45" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22373,11 +22373,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
+    <x:row r="46" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A46" s="91" t="str">
         <x:v>[ZW-ST-0603] 对开窗帘开停关交互</x:v>
       </x:c>
-      <x:c r="B46" s="91" t="str">
+      <x:c r="B46" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0603
 作为家庭成员，我能按左开、中停、右关控制两边一起运动的窗帘。
 Acceptance Criteria
@@ -22387,7 +22387,7 @@
 Dependencies
 - ZW-ST-1202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：对开窗帘开停关交互；检查“打开完成显示 0%，关闭完成显示 100%”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C46" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22420,11 +22420,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="47">
+    <x:row r="47" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A47" s="91" t="str">
         <x:v>[ZW-ST-0604] 卷帘开停关交互</x:v>
       </x:c>
-      <x:c r="B47" s="91" t="str">
+      <x:c r="B47" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0604
 作为家庭成员，我能按上开、中停、下关控制卷帘并在右侧看真实百分比。
 Acceptance Criteria
@@ -22434,7 +22434,7 @@
 Dependencies
 - ZW-ST-1202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：卷帘开停关交互；检查“开为 0%、关为 100%”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C47" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22467,11 +22467,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="48">
+    <x:row r="48" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A48" s="91" t="str">
         <x:v>[ZW-ST-0605] 鱼缸灯光与投食交互</x:v>
       </x:c>
-      <x:c r="B48" s="91" t="str">
+      <x:c r="B48" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0605
 作为家庭成员，我能选择灯光类型、开关灯并投食。
 Acceptance Criteria
@@ -22481,7 +22481,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：鱼缸灯光与投食交互；检查“投食期间按钮显示旋转状态且不可重复提交”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C48" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22514,11 +22514,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
+    <x:row r="49" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A49" s="91" t="str">
         <x:v>[ZW-ST-0606] 智能插座与用电统计</x:v>
       </x:c>
-      <x:c r="B49" s="91" t="str">
+      <x:c r="B49" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0606
 作为家庭成员，我能控制插座并查看日、周、月用电。
 Acceptance Criteria
@@ -22528,7 +22528,7 @@
 Dependencies
 - ZW-ST-1503
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：智能插座与用电统计；检查“统计口径和更新时间可见”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C49" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22561,11 +22561,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="50">
+    <x:row r="50" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A50" s="91" t="str">
         <x:v>[ZW-ST-0607] 路由器安全重启</x:v>
       </x:c>
-      <x:c r="B50" s="91" t="str">
+      <x:c r="B50" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0607
 作为管理员，我能用与普通开关不同的控件重启路由器。
 Acceptance Criteria
@@ -22575,7 +22575,7 @@
 Dependencies
 - ZW-ST-1503,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：路由器安全重启；检查“点击后显示影响范围与预计离线时间”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C50" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22608,11 +22608,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="51">
+    <x:row r="51" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A51" s="91" t="str">
         <x:v>[ZW-ST-0608] 扫地机器人全屋清洁快捷操作</x:v>
       </x:c>
-      <x:c r="B51" s="91" t="str">
+      <x:c r="B51" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0608
 作为家庭成员，我能从首页开始全屋清洁，复杂设置留在详情页。
 Acceptance Criteria
@@ -22622,7 +22622,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：扫地机器人全屋清洁快捷操作；检查“首页仅有全屋清洁”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C51" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22655,11 +22655,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="52">
+    <x:row r="52" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A52" s="91" t="str">
         <x:v>[ZW-ST-0609] 长按语音设备指令</x:v>
       </x:c>
-      <x:c r="B52" s="91" t="str">
+      <x:c r="B52" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0609
 作为家庭成员，我能长按对小米 Sound 或升降衣架说出指令。
 Acceptance Criteria
@@ -22669,7 +22669,7 @@
 Dependencies
 - ZW-ST-1502
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：长按语音设备指令；检查“界面明确提示按住说话”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C52" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22702,11 +22702,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
+    <x:row r="53" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A53" s="91" t="str">
         <x:v>[ZW-ST-0610] 个人电子设备只读状态</x:v>
       </x:c>
-      <x:c r="B53" s="91" t="str">
+      <x:c r="B53" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0610
 作为家庭成员，我能查看手机、平板和电脑在线状态而不会看到误导性的电源开关。
 Acceptance Criteria
@@ -22716,7 +22716,7 @@
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：个人电子设备只读状态；检查“卡片仅展示在线、网络和最后心跳”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C53" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22749,11 +22749,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="54">
+    <x:row r="54" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A54" s="91" t="str">
         <x:v>[ZW-ST-0611] 中枢额度与数据中心指标卡</x:v>
       </x:c>
-      <x:c r="B54" s="91" t="str">
+      <x:c r="B54" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0611
 作为管理员，我能查看 AI 用量、余额、服务数和 NAS 资源状态。
 Acceptance Criteria
@@ -22763,7 +22763,7 @@
 Dependencies
 - ZW-ST-1602
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：中枢额度与数据中心指标卡；检查“额度显示 5 小时、周限额和预充值余额及更新时间”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C54" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22796,11 +22796,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="55">
+    <x:row r="55" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A55" s="91" t="str">
         <x:v>[ZW-ST-0701] 四档响应式网格</x:v>
       </x:c>
-      <x:c r="B55" s="91" t="str">
+      <x:c r="B55" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0701
 作为家庭成员，我在不同屏幕和旋转方向下都能顺畅浏览和操作。
 Acceptance Criteria
@@ -22810,7 +22810,7 @@
 Dependencies
 - ZW-ST-0501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：四档响应式网格；检查“折叠外屏压缩为单列重点信息”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C55" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22843,11 +22843,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="56">
+    <x:row r="56" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A56" s="91" t="str">
         <x:v>[ZW-ST-0702] 无限信息流与侧边栏版权</x:v>
       </x:c>
-      <x:c r="B56" s="91" t="str">
+      <x:c r="B56" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0702
 作为手机用户，我能持续向下浏览所有房间而不被固定页脚截断。
 Acceptance Criteria
@@ -22857,7 +22857,7 @@
 Dependencies
 - ZW-ST-0701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：无限信息流与侧边栏版权；检查“主内容自然滚动”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C56" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22890,11 +22890,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="57">
+    <x:row r="57" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A57" s="91" t="str">
         <x:v>[ZW-ST-0703] 键盘、读屏与减少动态效果</x:v>
       </x:c>
-      <x:c r="B57" s="91" t="str">
+      <x:c r="B57" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0703
 作为有辅助需求的用户，我能不用精细触控完成核心操作。
 Acceptance Criteria
@@ -22904,7 +22904,7 @@
 Dependencies
 - ZW-ST-0701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：键盘、读屏与减少动态效果；检查“控件有可访问名称和焦点顺序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C57" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22937,11 +22937,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="58">
+    <x:row r="58" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A58" s="91" t="str">
         <x:v>[ZW-ST-0801] 添加单设备动作卡</x:v>
       </x:c>
-      <x:c r="B58" s="91" t="str">
+      <x:c r="B58" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0801
 作为场景作者，我能选择一个设备和 Action 生成一个步骤卡。
 Acceptance Criteria
@@ -22951,7 +22951,7 @@
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：添加单设备动作卡；检查“只能选择设备已注册的动作”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C58" s="91" t="str">
         <x:v>Feature</x:v>
@@ -22984,11 +22984,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="59">
+    <x:row r="59" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A59" s="91" t="str">
         <x:v>[ZW-ST-0802] 在一张卡中组合并行动作</x:v>
       </x:c>
-      <x:c r="B59" s="91" t="str">
+      <x:c r="B59" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0802
 作为场景作者，我能把客厅灯调暗和餐厅灯关闭放进同一并行步骤。
 Acceptance Criteria
@@ -22998,7 +22998,7 @@
 Dependencies
 - ZW-ST-0801
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：在一张卡中组合并行动作；检查“同卡动作无依赖时并行执行”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C59" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23031,11 +23031,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="60">
+    <x:row r="60" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A60" s="91" t="str">
         <x:v>[ZW-ST-0803] 步骤排序与依赖校验</x:v>
       </x:c>
-      <x:c r="B60" s="91" t="str">
+      <x:c r="B60" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0803
 作为场景作者，我能调整步骤顺序并在发布前发现循环或缺失依赖。
 Acceptance Criteria
@@ -23045,7 +23045,7 @@
 Dependencies
 - ZW-ST-0802
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：步骤排序与依赖校验；检查“支持拖动和键盘排序”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C60" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23078,11 +23078,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="61">
+    <x:row r="61" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A61" s="91" t="str">
         <x:v>[ZW-ST-0804] 场景草稿、Review 与发布</x:v>
       </x:c>
-      <x:c r="B61" s="91" t="str">
+      <x:c r="B61" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0804
 作为场景作者，我能在草稿中修改流程，由人确认后发布可执行版本。
 Acceptance Criteria
@@ -23092,7 +23092,7 @@
 Dependencies
 - ZW-ST-0803
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 组件/可访问性/响应式测试：场景草稿、Review 与发布；检查“草稿和已发布版本分离”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C61" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23125,11 +23125,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="62">
+    <x:row r="62" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A62" s="91" t="str">
         <x:v>[ZW-ST-0901] 观影模式预置场景</x:v>
       </x:c>
-      <x:c r="B62" s="91" t="str">
+      <x:c r="B62" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0901
 作为家庭成员，我能一键进入观影模式并看到六个步骤的执行结果。
 Acceptance Criteria
@@ -23139,7 +23139,7 @@
 Dependencies
 - ZW-ST-0804,ZW-ST-1101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 场景走查/指标验收：观影模式预置场景；检查“包含窗帘、灯、电视、Apple TV/Infuse、NAS 推荐和语音播报”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C62" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23172,11 +23172,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="63">
+    <x:row r="63" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A63" s="91" t="str">
         <x:v>[ZW-ST-0902] 离家模式预置场景</x:v>
       </x:c>
-      <x:c r="B63" s="91" t="str">
+      <x:c r="B63" s="92" t="str">
         <x:v>Logical ID: ZW-ST-0902
 作为家庭成员，我能检查并关闭所有获授权的灯、空调、新风、电视和 Apple TV。
 Acceptance Criteria
@@ -23186,7 +23186,7 @@
 Dependencies
 - ZW-ST-0804,ZW-ST-1101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 场景走查/指标验收：离家模式预置场景；检查“按能力发现目标而非写死设备清单”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C63" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23219,11 +23219,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="64">
+    <x:row r="64" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A64" s="91" t="str">
         <x:v>[ZW-ST-1001] 自然语言生成场景草稿</x:v>
       </x:c>
-      <x:c r="B64" s="91" t="str">
+      <x:c r="B64" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1001
 作为家庭成员，我描述想要的家庭场景后能得到可编辑步骤卡。
 Acceptance Criteria
@@ -23233,7 +23233,7 @@
 Dependencies
 - ZW-ST-1401,ZW-ST-0801
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：自然语言生成场景草稿；检查“系统展示解析出的意图、设备、动作和假设”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C64" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23266,11 +23266,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="65">
+    <x:row r="65" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A65" s="91" t="str">
         <x:v>[ZW-ST-1002] Skill 匹配与 Plan Mode 分流</x:v>
       </x:c>
-      <x:c r="B65" s="91" t="str">
+      <x:c r="B65" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1002
 作为家庭成员，我的简单请求使用已验证 Skill，复杂请求进入 Plan Mode。
 Acceptance Criteria
@@ -23280,7 +23280,7 @@
 Dependencies
 - ZW-ST-1402
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：Skill 匹配与 Plan Mode 分流；检查“路由结果含匹配依据和置信度”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C65" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23313,11 +23313,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="66">
+    <x:row r="66" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A66" s="91" t="str">
         <x:v>[ZW-ST-1003] 下载电影长程工作流</x:v>
       </x:c>
-      <x:c r="B66" s="91" t="str">
+      <x:c r="B66" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1003
 作为家庭成员，我能要求下载指定片名的 4K 杜比视界版本并在完成后收到通知。
 Acceptance Criteria
@@ -23327,7 +23327,7 @@
 Dependencies
 - ZW-ST-1303,ZW-ST-1103
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：下载电影长程工作流；检查“计划调用 NAS 搜索 MCP、过滤候选、下载 MCP、等待完成和微信通知”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C66" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23360,21 +23360,21 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="67">
+    <x:row r="67" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A67" s="91" t="str">
         <x:v>[ZW-ST-1101] 逐卡执行并展示结果</x:v>
       </x:c>
-      <x:c r="B67" s="91" t="str">
+      <x:c r="B67" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1101
 作为家庭成员，我触发场景后能看到每张卡和卡内动作的实时状态。
 Acceptance Criteria
-- 状态包含等待、运行、成功、失败、跳过和待确认；页面刷新后能恢复同一运行实例。
+- 状态包含等待、运行、成功、失败、跳过和待确认；页面刷新后能恢复同一运行实例；已发布场景完整执行成功率 ≥ 95%，失败步骤可定位。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-1201,ZW-ST-0302
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：逐卡执行并展示结果；检查“状态包含等待、运行、成功、失败、跳过和待确认”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C67" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23407,11 +23407,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="68">
+    <x:row r="68" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A68" s="91" t="str">
         <x:v>[ZW-ST-1102] 失败策略、重试与取消</x:v>
       </x:c>
-      <x:c r="B68" s="91" t="str">
+      <x:c r="B68" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1102
 作为家庭成员，我能理解失败原因，并在安全条件下重试或取消剩余步骤。
 Acceptance Criteria
@@ -23421,7 +23421,7 @@
 Dependencies
 - ZW-ST-1101
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：失败策略、重试与取消；检查“错误码映射为可行动说明”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C68" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23454,11 +23454,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="69">
+    <x:row r="69" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A69" s="91" t="str">
         <x:v>[ZW-ST-1103] 长程流程断点续跑</x:v>
       </x:c>
-      <x:c r="B69" s="91" t="str">
+      <x:c r="B69" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1103
 作为家庭成员，我的下载或清洁流程在服务重启后仍能继续或安全恢复。
 Acceptance Criteria
@@ -23468,7 +23468,7 @@
 Dependencies
 - ZW-ST-1203
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：长程流程断点续跑；检查“关键节点写入 checkpointer”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C69" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23501,11 +23501,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="70">
+    <x:row r="70" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A70" s="91" t="str">
         <x:v>[ZW-ST-1201] 统一异步任务契约</x:v>
       </x:c>
-      <x:c r="B70" s="91" t="str">
+      <x:c r="B70" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1201
 作为系统开发者，我能用同一契约创建、查询、取消和审计设备任务。
 Acceptance Criteria
@@ -23515,7 +23515,7 @@
 Dependencies
 - ZW-ST-0202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：统一异步任务契约；检查“任务含 idempotency_key、发起者、目标、参数、风险、超时、重试、trace_id 和标准状态机”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C70" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23548,11 +23548,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
+    <x:row r="71" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A71" s="91" t="str">
         <x:v>[ZW-ST-1202] 优先队列强制状态上报</x:v>
       </x:c>
-      <x:c r="B71" s="91" t="str">
+      <x:c r="B71" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1202
 作为家庭成员，我操作窗帘等过程敏感设备时能优先获得阶段反馈。
 Acceptance Criteria
@@ -23562,7 +23562,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：优先队列强制状态上报；检查“优先队列拒绝同步任务”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C71" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23595,11 +23595,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="72">
+    <x:row r="72" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A72" s="91" t="str">
         <x:v>[ZW-ST-1203] 超时、重试和死信恢复</x:v>
       </x:c>
-      <x:c r="B72" s="91" t="str">
+      <x:c r="B72" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1203
 作为运维者，我能处理设备无响应、瞬时故障和永久失败。
 Acceptance Criteria
@@ -23609,7 +23609,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：超时、重试和死信恢复；检查“重试次数与退避可配置”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C72" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23642,11 +23642,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="73">
+    <x:row r="73" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A73" s="91" t="str">
         <x:v>[ZW-ST-1204] 任务队列双视图</x:v>
       </x:c>
-      <x:c r="B73" s="91" t="str">
+      <x:c r="B73" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1204
 作为管理员，我能分别查看普通队列和优先队列的积压、运行与失败。
 Acceptance Criteria
@@ -23656,7 +23656,7 @@
 Dependencies
 - ZW-ST-1202
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：任务队列双视图；检查“两类队列可筛选”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C73" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23689,11 +23689,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="74">
+    <x:row r="74" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A74" s="91" t="str">
         <x:v>[ZW-ST-1301] MCP 工具发现与能力白名单</x:v>
       </x:c>
-      <x:c r="B74" s="91" t="str">
+      <x:c r="B74" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1301
 作为 Agent，我只能发现当前成员和场景被允许调用的工具。
 Acceptance Criteria
@@ -23703,7 +23703,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：MCP 工具发现与能力白名单；检查“网关按身份、角色、设备和风险返回白名单”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C74" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23736,11 +23736,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="75">
+    <x:row r="75" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A75" s="91" t="str">
         <x:v>[ZW-ST-1302] 设备适配器标准接口</x:v>
       </x:c>
-      <x:c r="B75" s="91" t="str">
+      <x:c r="B75" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1302
 作为适配器开发者，我能实现发现、读状态、执行动作、订阅事件和健康检查。
 Acceptance Criteria
@@ -23750,7 +23750,7 @@
 Dependencies
 - ZW-ST-0201,ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：设备适配器标准接口；检查“接口有契约测试”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C75" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23783,11 +23783,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="76">
+    <x:row r="76" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A76" s="91" t="str">
         <x:v>[ZW-ST-1303] 首批真实服务与设备接入</x:v>
       </x:c>
-      <x:c r="B76" s="91" t="str">
+      <x:c r="B76" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1303
 作为家庭成员，我能通过中枢使用窗帘、灯、插座、NAS 和中枢指标。
 Acceptance Criteria
@@ -23797,7 +23797,7 @@
 Dependencies
 - ZW-ST-1302
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 契约/集成/故障测试：首批真实服务与设备接入；检查“至少 5 类真实接入通过读写/只读能力声明”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C76" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23830,11 +23830,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="77">
+    <x:row r="77" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A77" s="91" t="str">
         <x:v>[ZW-ST-1401] 意图与风险分级</x:v>
       </x:c>
-      <x:c r="B77" s="91" t="str">
+      <x:c r="B77" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1401
 作为平台，我能将请求分类为 read、draft、write 或 high-risk 并选择处理路径。
 Acceptance Criteria
@@ -23844,7 +23844,7 @@
 Dependencies
 - ZW-ST-1503
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：意图与风险分级；检查“分类结果可解释且进入审计”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C77" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23877,11 +23877,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="78">
+    <x:row r="78" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A78" s="91" t="str">
         <x:v>[ZW-ST-1402] Planner 生成受约束任务图</x:v>
       </x:c>
-      <x:c r="B78" s="91" t="str">
+      <x:c r="B78" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1402
 作为家庭成员，我能获得有步骤、依赖、工具、预算和停止条件的计划。
 Acceptance Criteria
@@ -23891,7 +23891,7 @@
 Dependencies
 - ZW-ST-1401,ZW-ST-1301
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：Planner 生成受约束任务图；检查“计划无循环”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C78" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23924,11 +23924,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="79">
+    <x:row r="79" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A79" s="91" t="str">
         <x:v>[ZW-ST-1403] 计划人工审阅与修改</x:v>
       </x:c>
-      <x:c r="B79" s="91" t="str">
+      <x:c r="B79" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1403
 作为家庭成员，我能在执行前修改目标、参数、顺序和确认点。
 Acceptance Criteria
@@ -23938,7 +23938,7 @@
 Dependencies
 - ZW-ST-1402
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 计划评测/权限/工具集成测试：计划人工审阅与修改；检查“修改后重新校验权限与依赖”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C79" s="91" t="str">
         <x:v>Feature</x:v>
@@ -23971,11 +23971,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="80">
+    <x:row r="80" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A80" s="91" t="str">
         <x:v>[ZW-ST-1501] 端到端身份透传与工具侧鉴权</x:v>
       </x:c>
-      <x:c r="B80" s="91" t="str">
+      <x:c r="B80" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1501
 作为管理员，我能确保每次设备调用都以真实家庭成员身份授权。
 Acceptance Criteria
@@ -23985,7 +23985,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：端到端身份透传与工具侧鉴权；检查“OIDC→会话→JWT→Agent→MCP→数据层身份不断链”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C80" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24016,11 +24016,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="81">
+    <x:row r="81" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A81" s="91" t="str">
         <x:v>[ZW-ST-1502] 角色与儿童策略</x:v>
       </x:c>
-      <x:c r="B81" s="91" t="str">
+      <x:c r="B81" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1502
 作为管理员，我能为 admin、adult、kid 配置可见设备、动作和时间限制。
 Acceptance Criteria
@@ -24030,7 +24030,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：角色与儿童策略；检查“kid 请求强制经过 Compliance”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C81" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24063,21 +24063,21 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="82">
+    <x:row r="82" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A82" s="91" t="str">
         <x:v>[ZW-ST-1503] 高风险动作 prepare/confirm/execute</x:v>
       </x:c>
-      <x:c r="B82" s="91" t="str">
+      <x:c r="B82" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1503
 作为家庭成员，我在重启路由器或断开关键插座前能看到影响并明确确认。
 Acceptance Criteria
-- 准备阶段返回影响范围和确认令牌；令牌短期有效且绑定参数；执行与确认人都被审计。
+- 准备阶段返回影响范围和确认令牌；令牌短期有效且绑定参数；执行与确认人都被审计；100% 高风险动作在执行前完成明确确认，确认令牌绑定动作参数。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：高风险动作 prepare/confirm/execute；检查“准备阶段返回影响范围和确认令牌”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C82" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24110,11 +24110,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="83">
+    <x:row r="83" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A83" s="91" t="str">
         <x:v>[ZW-ST-1504] 不可变审计查询</x:v>
       </x:c>
-      <x:c r="B83" s="91" t="str">
+      <x:c r="B83" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1504
 作为管理员，我能按成员、设备、任务和 trace 查询谁在何时做了什么。
 Acceptance Criteria
@@ -24124,7 +24124,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 安全策略/越权/审计测试：不可变审计查询；检查“审计事件追加写”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C83" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24157,11 +24157,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="84">
+    <x:row r="84" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A84" s="91" t="str">
         <x:v>[ZW-ST-1601] 全链路 trace 关联</x:v>
       </x:c>
-      <x:c r="B84" s="91" t="str">
+      <x:c r="B84" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1601
 作为运维者，我能从页面任务追到 Agent、MCP、适配器和设备事件。
 Acceptance Criteria
@@ -24171,7 +24171,7 @@
 Dependencies
 - ZW-ST-1201
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：全链路 trace 关联；检查“各层共享 trace_id”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C84" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24204,11 +24204,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="85">
+    <x:row r="85" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A85" s="91" t="str">
         <x:v>[ZW-ST-1602] 模型用量与预算面板</x:v>
       </x:c>
-      <x:c r="B85" s="91" t="str">
+      <x:c r="B85" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1602
 作为管理员，我能查看 ChatGPT Plus 5 小时/周用量、预充值余额和任务成本。
 Acceptance Criteria
@@ -24218,7 +24218,7 @@
 Dependencies
 - ZW-ST-1601
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：模型用量与预算面板；检查“每个指标显示来源、时间和不可用状态”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C85" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24251,11 +24251,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="86">
+    <x:row r="86" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A86" s="91" t="str">
         <x:v>[ZW-ST-1603] 家庭基础设施健康面板</x:v>
       </x:c>
-      <x:c r="B86" s="91" t="str">
+      <x:c r="B86" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1603
 作为管理员，我能查看树莓派和 NAS 的服务、CPU、内存、磁盘、温度和告警。
 Acceptance Criteria
@@ -24265,7 +24265,7 @@
 Dependencies
 - ZW-ST-1601
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：家庭基础设施健康面板；检查“指标带时间窗”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C86" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24298,11 +24298,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="87">
+    <x:row r="87" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A87" s="91" t="str">
         <x:v>[ZW-ST-1701] 稳定需求 ID 与父子关系</x:v>
       </x:c>
-      <x:c r="B87" s="91" t="str">
+      <x:c r="B87" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1701
 作为产品和 Agent，我能用不随 Jira/GitHub 迁移而改变的 ID 查找需求。
 Acceptance Criteria
@@ -24312,7 +24312,7 @@
 Dependencies
 - None
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：稳定需求 ID 与父子关系；检查“Roadmap、Epic、Story、Task ID 唯一”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C87" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24343,11 +24343,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="88">
+    <x:row r="88" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A88" s="91" t="str">
         <x:v>[ZW-ST-1702] Story 结构化契约</x:v>
       </x:c>
-      <x:c r="B88" s="91" t="str">
+      <x:c r="B88" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1702
 作为 AI Agent，我能从统一字段读取价值、范围、验收、依赖、风险和证据要求。
 Acceptance Criteria
@@ -24357,7 +24357,7 @@
 Dependencies
 - ZW-ST-1701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：Story 结构化契约；检查“必填字段有数据字典与枚举”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C88" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24390,21 +24390,21 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="89">
+    <x:row r="89" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A89" s="91" t="str">
         <x:v>[ZW-ST-1703] ADR/TC/BUG/PR/Release 追溯门禁</x:v>
       </x:c>
-      <x:c r="B89" s="91" t="str">
+      <x:c r="B89" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1703
 作为维护者，我能从 Story 找到架构决策、测试、缺陷、代码和发布。
 Acceptance Criteria
-- PR 必须引用 Story；架构变化必须引用 ADR；Done 前测试证据齐全且阻塞缺陷关闭。
+- PR 必须引用 Story；架构变化必须引用 ADR；Done 前测试证据齐全且阻塞缺陷关闭；100% 发布变更可回溯到 Story、测试证据、PR、版本和运行 trace。
 Non-goal
 - 不包含未写入验收标准的扩展能力。
 Dependencies
 - ZW-ST-1702
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：ADR/TC/BUG/PR/Release 追溯门禁；检查“PR 必须引用 Story”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C89" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24437,11 +24437,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="90">
+    <x:row r="90" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A90" s="91" t="str">
         <x:v>[ZW-ST-1704] Jira 与 GitHub 可移植导入视图</x:v>
       </x:c>
-      <x:c r="B90" s="91" t="str">
+      <x:c r="B90" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1704
 作为维护者，我能从同一需求源生成适配不同平台层级的导入数据。
 Acceptance Criteria
@@ -24451,7 +24451,7 @@
 Dependencies
 - ZW-ST-1701
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 需求门禁/导入/追溯回归：Jira 与 GitHub 可移植导入视图；检查“Jira Standard、Jira Advanced 和 GitHub 视图保留逻辑 ID”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C90" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24484,11 +24484,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="91">
+    <x:row r="91" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A91" s="91" t="str">
         <x:v>[ZW-ST-1801] NAS 容器化部署</x:v>
       </x:c>
-      <x:c r="B91" s="91" t="str">
+      <x:c r="B91" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1801
 作为管理员，我能在绿联 NAS 上用版本化配置部署 Web 和中枢服务。
 Acceptance Criteria
@@ -24498,7 +24498,7 @@
 Dependencies
 - ZW-ST-1501
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：NAS 容器化部署；检查“部署不依赖开发机”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C91" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24531,11 +24531,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="92">
+    <x:row r="92" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A92" s="91" t="str">
         <x:v>[ZW-ST-1802] 安全升级与回滚</x:v>
       </x:c>
-      <x:c r="B92" s="91" t="str">
+      <x:c r="B92" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1802
 作为管理员，我能在升级失败时恢复到上一可用版本和数据 Schema。
 Acceptance Criteria
@@ -24545,7 +24545,7 @@
 Dependencies
 - ZW-ST-1801
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：安全升级与回滚；检查“发布前备份”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C92" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24578,11 +24578,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="93">
+    <x:row r="93" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A93" s="91" t="str">
         <x:v>[ZW-ST-1803] 局域网降级与灾难恢复</x:v>
       </x:c>
-      <x:c r="B93" s="91" t="str">
+      <x:c r="B93" s="92" t="str">
         <x:v>Logical ID: ZW-ST-1803
 作为家庭成员，我在公网中断时仍能使用核心控制；节点故障后数据可恢复。
 Acceptance Criteria
@@ -24592,7 +24592,7 @@
 Dependencies
 - ZW-ST-1801,ZW-ST-1203
 Verification
-- 自动化测试 + 原型或真实设备验收</x:v>
+- 部署/升级/回滚/恢复演练：局域网降级与灾难恢复；检查“核心控制不依赖公网”；证据：TC、PR、trace_id。</x:v>
       </x:c>
       <x:c r="C93" s="91" t="str">
         <x:v>Feature</x:v>
@@ -24625,11 +24625,11 @@
         <x:v>待关联 TC / PR / Release / trace_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="94">
+    <x:row r="94" ht="198" hidden="0" customHeight="1">
       <x:c r="A94" s="91" t="str">
         <x:v>[ZW-TK-0201-A] 编写 Device Profile JSON Schema</x:v>
       </x:c>
-      <x:c r="B94" s="91" t="str">
+      <x:c r="B94" s="92" t="str">
         <x:v>Logical ID: ZW-TK-0201-A
 定义状态、动作、参数、风险、UI hint 和版本字段。
 Acceptance Criteria
@@ -24668,11 +24668,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="95">
+    <x:row r="95" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A95" s="91" t="str">
         <x:v>[ZW-TK-0201-B] 补齐 12 类设备示例</x:v>
       </x:c>
-      <x:c r="B95" s="91" t="str">
+      <x:c r="B95" s="92" t="str">
         <x:v>Logical ID: ZW-TK-0201-B
 为空调、灯、窗帘、卷帘、鱼缸、插座、路由器、扫地机、语音设备、终端、中枢和 NAS 建样例。
 Acceptance Criteria
@@ -24711,11 +24711,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="96">
+    <x:row r="96" ht="198" hidden="0" customHeight="1">
       <x:c r="A96" s="91" t="str">
         <x:v>[ZW-TK-0603-A] 实现窗帘运动态组件</x:v>
       </x:c>
-      <x:c r="B96" s="91" t="str">
+      <x:c r="B96" s="92" t="str">
         <x:v>Logical ID: ZW-TK-0603-A
 加入开/停/关、运动动画和百分比隐藏逻辑。
 Acceptance Criteria
@@ -24754,11 +24754,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="97">
+    <x:row r="97" ht="198" hidden="0" customHeight="1">
       <x:c r="A97" s="91" t="str">
         <x:v>[ZW-TK-1201-A] 定义任务与事件 Schema</x:v>
       </x:c>
-      <x:c r="B97" s="91" t="str">
+      <x:c r="B97" s="92" t="str">
         <x:v>Logical ID: ZW-TK-1201-A
 固化状态机、幂等键、错误、重试和 trace 字段。
 Acceptance Criteria
@@ -24797,11 +24797,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="98">
+    <x:row r="98" ht="198" hidden="0" customHeight="1">
       <x:c r="A98" s="91" t="str">
         <x:v>[ZW-TK-1202-A] 配置优先队列与消费者</x:v>
       </x:c>
-      <x:c r="B98" s="91" t="str">
+      <x:c r="B98" s="92" t="str">
         <x:v>Logical ID: ZW-TK-1202-A
 创建隔离队列、并发、限流和状态上报约束。
 Acceptance Criteria
@@ -24840,11 +24840,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="99">
+    <x:row r="99" ht="198" hidden="0" customHeight="1">
       <x:c r="A99" s="91" t="str">
         <x:v>[ZW-TK-1302-A] 建立适配器契约测试套件</x:v>
       </x:c>
-      <x:c r="B99" s="91" t="str">
+      <x:c r="B99" s="92" t="str">
         <x:v>Logical ID: ZW-TK-1302-A
 测试发现、读状态、动作、事件、健康和错误映射。
 Acceptance Criteria
@@ -24883,11 +24883,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="100">
+    <x:row r="100" ht="198" hidden="0" customHeight="1">
       <x:c r="A100" s="91" t="str">
         <x:v>[ZW-TK-1402-A] 定义 Planner 输出 Schema</x:v>
       </x:c>
-      <x:c r="B100" s="91" t="str">
+      <x:c r="B100" s="92" t="str">
         <x:v>Logical ID: ZW-TK-1402-A
 包含步骤、依赖、预算、确认点、回滚提示和停止条件。
 Acceptance Criteria
@@ -24926,11 +24926,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="101">
+    <x:row r="101" ht="198" hidden="0" customHeight="1">
       <x:c r="A101" s="91" t="str">
         <x:v>[ZW-TK-1503-A] 实现确认令牌服务</x:v>
       </x:c>
-      <x:c r="B101" s="91" t="str">
+      <x:c r="B101" s="92" t="str">
         <x:v>Logical ID: ZW-TK-1503-A
 令牌绑定用户、动作、参数、影响范围和短期过期时间。
 Acceptance Criteria
@@ -24969,11 +24969,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="102">
+    <x:row r="102" ht="198" hidden="0" customHeight="1">
       <x:c r="A102" s="91" t="str">
         <x:v>[ZW-TK-1601-A] 统一 trace_id 传播中间件</x:v>
       </x:c>
-      <x:c r="B102" s="91" t="str">
+      <x:c r="B102" s="92" t="str">
         <x:v>Logical ID: ZW-TK-1601-A
 覆盖 API、Planner、MCP、队列消费者和适配器。
 Acceptance Criteria
@@ -25012,11 +25012,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="103">
+    <x:row r="103" ht="198" hidden="0" customHeight="1">
       <x:c r="A103" s="91" t="str">
         <x:v>[ZW-TK-1702-A] 实现需求 Schema 校验器</x:v>
       </x:c>
-      <x:c r="B103" s="91" t="str">
+      <x:c r="B103" s="92" t="str">
         <x:v>Logical ID: ZW-TK-1702-A
 检查 ID、父子关系、枚举、必填字段和验收标准。
 Acceptance Criteria
@@ -25055,11 +25055,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="104">
+    <x:row r="104" ht="198" hidden="0" customHeight="1">
       <x:c r="A104" s="91" t="str">
         <x:v>[ZW-TK-1801-A] 固化 Compose 与密钥注入</x:v>
       </x:c>
-      <x:c r="B104" s="91" t="str">
+      <x:c r="B104" s="92" t="str">
         <x:v>Logical ID: ZW-TK-1801-A
 建立 Web/API/队列/数据库的部署声明和环境模板。
 Acceptance Criteria
@@ -25098,11 +25098,11 @@
         <x:v>待关联 commit / PR</x:v>
       </x:c>
     </x:row>
-    <x:row r="105">
+    <x:row r="105" ht="198" hidden="0" customHeight="1">
       <x:c r="A105" s="91" t="str">
         <x:v>[ZW-TK-1802-A] 执行一次回滚演练</x:v>
       </x:c>
-      <x:c r="B105" s="91" t="str">
+      <x:c r="B105" s="92" t="str">
         <x:v>Logical ID: ZW-TK-1802-A
 从升级失败恢复应用版本、配置和数据库。
 Acceptance Criteria
@@ -25144,7 +25144,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8978c3fca30047c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb5671d429f94bbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25747,7 +25747,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e83c97c3ac74785"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5fafe8bbe504a1c"/>
   </x:tableParts>
 </x:worksheet>
 </file>